--- a/events/Bratislava_2019_WC/Bratislava_2019_WC_start.xlsx
+++ b/events/Bratislava_2019_WC/Bratislava_2019_WC_start.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W605"/>
+  <dimension ref="A1:AC594"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,17 +519,47 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Name4</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Name5</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Name6</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
           <t>ICF_ID1</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>ICF_ID2</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>ICF_ID3</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>ICF_ID4</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>ICF_ID5</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>ICF_ID6</t>
         </is>
       </c>
     </row>
@@ -590,7 +620,7 @@
           <t>LEIBFARTH Evy</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>83538</t>
         </is>
@@ -653,7 +683,7 @@
           <t>NEE Ashley</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>36363</t>
         </is>
@@ -716,7 +746,7 @@
           <t>STANOVSKY Martin</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>68782</t>
         </is>
@@ -779,7 +809,7 @@
           <t>SHABANOV Maxim</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>40575</t>
         </is>
@@ -842,7 +872,7 @@
           <t>STANOVSKY Samuel</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>84121</t>
         </is>
@@ -905,7 +935,7 @@
           <t>GONCALVES Pedro</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>38017</t>
         </is>
@@ -968,7 +998,7 @@
           <t>WOS Michal</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>65063</t>
         </is>
@@ -1031,7 +1061,7 @@
           <t>KARLSSON Max</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>35111</t>
         </is>
@@ -1094,7 +1124,7 @@
           <t>SARAMANDIF Terence</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>79340</t>
         </is>
@@ -1157,7 +1187,7 @@
           <t>WAHLEN Fredrik</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>35102</t>
         </is>
@@ -1220,7 +1250,7 @@
           <t>YERENGAIPOV Kuanysh</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>42085</t>
         </is>
@@ -1283,7 +1313,7 @@
           <t>NEPOGODIN Aleksandr</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>39710</t>
         </is>
@@ -1346,7 +1376,7 @@
           <t>CHAPPELL Etienne</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>75833</t>
         </is>
@@ -1409,7 +1439,7 @@
           <t>ZAZIABLO Jaroslaw</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>75728</t>
         </is>
@@ -1472,7 +1502,7 @@
           <t>OTTEN Joris</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>41698</t>
         </is>
@@ -1535,7 +1565,7 @@
           <t>FARRELL Oisin</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>37916</t>
         </is>
@@ -1598,7 +1628,7 @@
           <t>KUZNETSOVA Daria</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>76780</t>
         </is>
@@ -1641,11 +1671,6 @@
       <c r="K19" t="n">
         <v>18</v>
       </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>N. N.</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2025,11 +2050,6 @@
       <c r="K27" t="n">
         <v>26</v>
       </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>N. N.</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2242,7 +2262,7 @@
           <t>XU Yongzhao</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>69446</t>
         </is>
@@ -2300,7 +2320,7 @@
           <t>ZOU Weijian</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>94208</t>
         </is>
@@ -2358,7 +2378,7 @@
           <t>HUANG Fa</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>87703</t>
         </is>
@@ -2416,7 +2436,7 @@
           <t>OZOLS Kriss</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>48993</t>
         </is>
@@ -2474,7 +2494,7 @@
           <t>YERENGAIPOV Kuanysh</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>42085</t>
         </is>
@@ -2532,7 +2552,7 @@
           <t>MIKHAILOV Igor</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>44026</t>
         </is>
@@ -2590,7 +2610,7 @@
           <t>CHAKIR Issam</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>75631</t>
         </is>
@@ -2701,7 +2721,7 @@
           <t>CARVALHO Jose</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>35486</t>
         </is>
@@ -2759,7 +2779,7 @@
           <t>CONEY William</t>
         </is>
       </c>
-      <c r="U40" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>53138</t>
         </is>
@@ -2817,7 +2837,7 @@
           <t>GIBBONS James</t>
         </is>
       </c>
-      <c r="U41" t="inlineStr">
+      <c r="X41" t="inlineStr">
         <is>
           <t>77314</t>
         </is>
@@ -2875,7 +2895,7 @@
           <t>AMANBAYEV Adil</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr">
+      <c r="X42" t="inlineStr">
         <is>
           <t>68999</t>
         </is>
@@ -2933,7 +2953,7 @@
           <t>SARAMANDIF Terence</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr">
+      <c r="X43" t="inlineStr">
         <is>
           <t>79340</t>
         </is>
@@ -2991,7 +3011,7 @@
           <t>MICOZZI Flavio</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr">
+      <c r="X44" t="inlineStr">
         <is>
           <t>77363</t>
         </is>
@@ -3049,7 +3069,7 @@
           <t>OTTEN Joris</t>
         </is>
       </c>
-      <c r="U45" t="inlineStr">
+      <c r="X45" t="inlineStr">
         <is>
           <t>41698</t>
         </is>
@@ -3107,7 +3127,7 @@
           <t>TANIGUCHI Kazuya</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr">
+      <c r="X46" t="inlineStr">
         <is>
           <t>39699</t>
         </is>
@@ -3165,7 +3185,7 @@
           <t>POTOCNY Marcel</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr">
+      <c r="X47" t="inlineStr">
         <is>
           <t>35235</t>
         </is>
@@ -3223,7 +3243,7 @@
           <t>HEGER Vojtech</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr">
+      <c r="X48" t="inlineStr">
         <is>
           <t>68872</t>
         </is>
@@ -3281,7 +3301,7 @@
           <t>KULIKOV Alexandr</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr">
+      <c r="X49" t="inlineStr">
         <is>
           <t>39679</t>
         </is>
@@ -3339,7 +3359,7 @@
           <t>WASHER Patrick</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr">
+      <c r="X50" t="inlineStr">
         <is>
           <t>42081</t>
         </is>
@@ -3450,7 +3470,7 @@
           <t>GIBB Benjamin</t>
         </is>
       </c>
-      <c r="U52" t="inlineStr">
+      <c r="X52" t="inlineStr">
         <is>
           <t>36711</t>
         </is>
@@ -3508,7 +3528,7 @@
           <t>SHKLIARUK Nikolai</t>
         </is>
       </c>
-      <c r="U53" t="inlineStr">
+      <c r="X53" t="inlineStr">
         <is>
           <t>44025</t>
         </is>
@@ -3566,7 +3586,7 @@
           <t>LOWTHER Steven</t>
         </is>
       </c>
-      <c r="U54" t="inlineStr">
+      <c r="X54" t="inlineStr">
         <is>
           <t>44811</t>
         </is>
@@ -3624,7 +3644,7 @@
           <t>BOURHIS Jean Pierre</t>
         </is>
       </c>
-      <c r="U55" t="inlineStr">
+      <c r="X55" t="inlineStr">
         <is>
           <t>36968</t>
         </is>
@@ -3682,7 +3702,7 @@
           <t>SASAKI Shota</t>
         </is>
       </c>
-      <c r="U56" t="inlineStr">
+      <c r="X56" t="inlineStr">
         <is>
           <t>41610</t>
         </is>
@@ -3740,7 +3760,7 @@
           <t>NEPOGODIN Aleksandr</t>
         </is>
       </c>
-      <c r="U57" t="inlineStr">
+      <c r="X57" t="inlineStr">
         <is>
           <t>39710</t>
         </is>
@@ -3798,7 +3818,7 @@
           <t>ABBOTT Thomas</t>
         </is>
       </c>
-      <c r="U58" t="inlineStr">
+      <c r="X58" t="inlineStr">
         <is>
           <t>36514</t>
         </is>
@@ -3856,7 +3876,7 @@
           <t>BOURHIS Yves</t>
         </is>
       </c>
-      <c r="U59" t="inlineStr">
+      <c r="X59" t="inlineStr">
         <is>
           <t>63237</t>
         </is>
@@ -3914,7 +3934,7 @@
           <t>BORGES Felipe</t>
         </is>
       </c>
-      <c r="U60" t="inlineStr">
+      <c r="X60" t="inlineStr">
         <is>
           <t>38012</t>
         </is>
@@ -3972,7 +3992,7 @@
           <t>SZTUBA Igor</t>
         </is>
       </c>
-      <c r="U61" t="inlineStr">
+      <c r="X61" t="inlineStr">
         <is>
           <t>35087</t>
         </is>
@@ -4030,7 +4050,7 @@
           <t>ROSSI Sebastian</t>
         </is>
       </c>
-      <c r="U62" t="inlineStr">
+      <c r="X62" t="inlineStr">
         <is>
           <t>36915</t>
         </is>
@@ -4088,7 +4108,7 @@
           <t>LOKKEN Zachary</t>
         </is>
       </c>
-      <c r="U63" t="inlineStr">
+      <c r="X63" t="inlineStr">
         <is>
           <t>35069</t>
         </is>
@@ -4146,7 +4166,7 @@
           <t>RAK Tomas</t>
         </is>
       </c>
-      <c r="U64" t="inlineStr">
+      <c r="X64" t="inlineStr">
         <is>
           <t>35056</t>
         </is>
@@ -4204,7 +4224,7 @@
           <t>CECCON Paolo</t>
         </is>
       </c>
-      <c r="U65" t="inlineStr">
+      <c r="X65" t="inlineStr">
         <is>
           <t>39903</t>
         </is>
@@ -4262,7 +4282,7 @@
           <t>WATKINS Daniel</t>
         </is>
       </c>
-      <c r="U66" t="inlineStr">
+      <c r="X66" t="inlineStr">
         <is>
           <t>38430</t>
         </is>
@@ -4320,7 +4340,7 @@
           <t>SZTUBA Kacper</t>
         </is>
       </c>
-      <c r="U67" t="inlineStr">
+      <c r="X67" t="inlineStr">
         <is>
           <t>53636</t>
         </is>
@@ -4378,7 +4398,7 @@
           <t>BADURA Jergus</t>
         </is>
       </c>
-      <c r="U68" t="inlineStr">
+      <c r="X68" t="inlineStr">
         <is>
           <t>68767</t>
         </is>
@@ -4436,7 +4456,7 @@
           <t>BORROWS Ian</t>
         </is>
       </c>
-      <c r="U69" t="inlineStr">
+      <c r="X69" t="inlineStr">
         <is>
           <t>36534</t>
         </is>
@@ -4494,7 +4514,7 @@
           <t>KOECHLIN Thomas</t>
         </is>
       </c>
-      <c r="U70" t="inlineStr">
+      <c r="X70" t="inlineStr">
         <is>
           <t>35419</t>
         </is>
@@ -4552,7 +4572,7 @@
           <t>HANEDA Takuya</t>
         </is>
       </c>
-      <c r="U71" t="inlineStr">
+      <c r="X71" t="inlineStr">
         <is>
           <t>36481</t>
         </is>
@@ -4610,7 +4630,7 @@
           <t>TRAVE Miquel</t>
         </is>
       </c>
-      <c r="U72" t="inlineStr">
+      <c r="X72" t="inlineStr">
         <is>
           <t>68998</t>
         </is>
@@ -4668,7 +4688,7 @@
           <t>EICHFELD Casey</t>
         </is>
       </c>
-      <c r="U73" t="inlineStr">
+      <c r="X73" t="inlineStr">
         <is>
           <t>35067</t>
         </is>
@@ -4726,7 +4746,7 @@
           <t>JOLY Cedric</t>
         </is>
       </c>
-      <c r="U74" t="inlineStr">
+      <c r="X74" t="inlineStr">
         <is>
           <t>35681</t>
         </is>
@@ -4784,7 +4804,7 @@
           <t>ELOSEGI Ander</t>
         </is>
       </c>
-      <c r="U75" t="inlineStr">
+      <c r="X75" t="inlineStr">
         <is>
           <t>35785</t>
         </is>
@@ -4842,7 +4862,7 @@
           <t>BERCIC Anze</t>
         </is>
       </c>
-      <c r="U76" t="inlineStr">
+      <c r="X76" t="inlineStr">
         <is>
           <t>36253</t>
         </is>
@@ -4900,7 +4920,7 @@
           <t>HEDWIG Grzegorz</t>
         </is>
       </c>
-      <c r="U77" t="inlineStr">
+      <c r="X77" t="inlineStr">
         <is>
           <t>35465</t>
         </is>
@@ -4958,7 +4978,7 @@
           <t>ROHAN Lukas</t>
         </is>
       </c>
-      <c r="U78" t="inlineStr">
+      <c r="X78" t="inlineStr">
         <is>
           <t>36114</t>
         </is>
@@ -5016,7 +5036,7 @@
           <t>THOMAS Martin</t>
         </is>
       </c>
-      <c r="U79" t="inlineStr">
+      <c r="X79" t="inlineStr">
         <is>
           <t>35412</t>
         </is>
@@ -5074,7 +5094,7 @@
           <t>GARGAUD CHANUT Denis</t>
         </is>
       </c>
-      <c r="U80" t="inlineStr">
+      <c r="X80" t="inlineStr">
         <is>
           <t>35177</t>
         </is>
@@ -5132,7 +5152,7 @@
           <t>MARTIKAN Michal</t>
         </is>
       </c>
-      <c r="U81" t="inlineStr">
+      <c r="X81" t="inlineStr">
         <is>
           <t>35365</t>
         </is>
@@ -5190,7 +5210,7 @@
           <t>BOZIC Luka</t>
         </is>
       </c>
-      <c r="U82" t="inlineStr">
+      <c r="X82" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
@@ -5248,7 +5268,7 @@
           <t>BENUS Matej</t>
         </is>
       </c>
-      <c r="U83" t="inlineStr">
+      <c r="X83" t="inlineStr">
         <is>
           <t>35353</t>
         </is>
@@ -5306,7 +5326,7 @@
           <t>ANTON Franz</t>
         </is>
       </c>
-      <c r="U84" t="inlineStr">
+      <c r="X84" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
@@ -5364,7 +5384,7 @@
           <t>SAVSEK Benjamin</t>
         </is>
       </c>
-      <c r="U85" t="inlineStr">
+      <c r="X85" t="inlineStr">
         <is>
           <t>36218</t>
         </is>
@@ -5422,7 +5442,7 @@
           <t>SLAFKOVSKY Alexander</t>
         </is>
       </c>
-      <c r="U86" t="inlineStr">
+      <c r="X86" t="inlineStr">
         <is>
           <t>35129</t>
         </is>
@@ -5480,7 +5500,7 @@
           <t>NICHOLAS Ella</t>
         </is>
       </c>
-      <c r="U87" t="inlineStr">
+      <c r="X87" t="inlineStr">
         <is>
           <t>36591</t>
         </is>
@@ -5538,7 +5558,7 @@
           <t>SORRIBES Laia</t>
         </is>
       </c>
-      <c r="U88" t="inlineStr">
+      <c r="X88" t="inlineStr">
         <is>
           <t>68822</t>
         </is>
@@ -5596,7 +5616,7 @@
           <t>SAFINA Kamilla</t>
         </is>
       </c>
-      <c r="U89" t="inlineStr">
+      <c r="X89" t="inlineStr">
         <is>
           <t>42095</t>
         </is>
@@ -5654,7 +5674,7 @@
           <t>KUZNETSOVA Daria</t>
         </is>
       </c>
-      <c r="U90" t="inlineStr">
+      <c r="X90" t="inlineStr">
         <is>
           <t>76780</t>
         </is>
@@ -5712,7 +5732,7 @@
           <t>NICHOLAS Jane</t>
         </is>
       </c>
-      <c r="U91" t="inlineStr">
+      <c r="X91" t="inlineStr">
         <is>
           <t>93757</t>
         </is>
@@ -5770,7 +5790,7 @@
           <t>THOMAS Hannah</t>
         </is>
       </c>
-      <c r="U92" t="inlineStr">
+      <c r="X92" t="inlineStr">
         <is>
           <t>85758</t>
         </is>
@@ -5828,7 +5848,7 @@
           <t>LEIBFARTH Evy</t>
         </is>
       </c>
-      <c r="U93" t="inlineStr">
+      <c r="X93" t="inlineStr">
         <is>
           <t>83538</t>
         </is>
@@ -5886,7 +5906,7 @@
           <t>OGILVIE Sophie</t>
         </is>
       </c>
-      <c r="U94" t="inlineStr">
+      <c r="X94" t="inlineStr">
         <is>
           <t>53134</t>
         </is>
@@ -5944,7 +5964,7 @@
           <t>RANDLE Kensa</t>
         </is>
       </c>
-      <c r="U95" t="inlineStr">
+      <c r="X95" t="inlineStr">
         <is>
           <t>51859</t>
         </is>
@@ -6002,7 +6022,7 @@
           <t>BETTERIDGE Lois</t>
         </is>
       </c>
-      <c r="U96" t="inlineStr">
+      <c r="X96" t="inlineStr">
         <is>
           <t>60078</t>
         </is>
@@ -6060,7 +6080,7 @@
           <t>MASLEN Amber</t>
         </is>
       </c>
-      <c r="U97" t="inlineStr">
+      <c r="X97" t="inlineStr">
         <is>
           <t>53074</t>
         </is>
@@ -6118,7 +6138,7 @@
           <t>MALEKOVA Arina</t>
         </is>
       </c>
-      <c r="U98" t="inlineStr">
+      <c r="X98" t="inlineStr">
         <is>
           <t>44024</t>
         </is>
@@ -6176,7 +6196,7 @@
           <t>MALAGUTI Francesca</t>
         </is>
       </c>
-      <c r="U99" t="inlineStr">
+      <c r="X99" t="inlineStr">
         <is>
           <t>77362</t>
         </is>
@@ -6234,7 +6254,7 @@
           <t>BRAENDLE Naemi</t>
         </is>
       </c>
-      <c r="U100" t="inlineStr">
+      <c r="X100" t="inlineStr">
         <is>
           <t>68845</t>
         </is>
@@ -6292,7 +6312,7 @@
           <t>MITASIKOVA Monika</t>
         </is>
       </c>
-      <c r="U101" t="inlineStr">
+      <c r="X101" t="inlineStr">
         <is>
           <t>75445</t>
         </is>
@@ -6350,7 +6370,7 @@
           <t>PELLICER CHICA Laura</t>
         </is>
       </c>
-      <c r="U102" t="inlineStr">
+      <c r="X102" t="inlineStr">
         <is>
           <t>43129</t>
         </is>
@@ -6408,7 +6428,7 @@
           <t>ITO Yoshika</t>
         </is>
       </c>
-      <c r="U103" t="inlineStr">
+      <c r="X103" t="inlineStr">
         <is>
           <t>36647</t>
         </is>
@@ -6466,7 +6486,7 @@
           <t>NEE Ashley</t>
         </is>
       </c>
-      <c r="U104" t="inlineStr">
+      <c r="X104" t="inlineStr">
         <is>
           <t>36363</t>
         </is>
@@ -6524,7 +6544,7 @@
           <t>VILARRUBLA Nuria</t>
         </is>
       </c>
-      <c r="U105" t="inlineStr">
+      <c r="X105" t="inlineStr">
         <is>
           <t>35746</t>
         </is>
@@ -6582,7 +6602,7 @@
           <t>TAKESHITA Yuriko</t>
         </is>
       </c>
-      <c r="U106" t="inlineStr">
+      <c r="X106" t="inlineStr">
         <is>
           <t>36487</t>
         </is>
@@ -6640,7 +6660,7 @@
           <t>APEL Elena</t>
         </is>
       </c>
-      <c r="U107" t="inlineStr">
+      <c r="X107" t="inlineStr">
         <is>
           <t>51837</t>
         </is>
@@ -6698,7 +6718,7 @@
           <t>LEENDERS Claudia</t>
         </is>
       </c>
-      <c r="U108" t="inlineStr">
+      <c r="X108" t="inlineStr">
         <is>
           <t>35331</t>
         </is>
@@ -6756,7 +6776,7 @@
           <t>HAMER-EVANS Megan</t>
         </is>
       </c>
-      <c r="U109" t="inlineStr">
+      <c r="X109" t="inlineStr">
         <is>
           <t>55138</t>
         </is>
@@ -6814,7 +6834,7 @@
           <t>TEUNISSEN Lena</t>
         </is>
       </c>
-      <c r="U110" t="inlineStr">
+      <c r="X110" t="inlineStr">
         <is>
           <t>35344</t>
         </is>
@@ -6872,7 +6892,7 @@
           <t>FOX Noemie</t>
         </is>
       </c>
-      <c r="U111" t="inlineStr">
+      <c r="X111" t="inlineStr">
         <is>
           <t>44812</t>
         </is>
@@ -6930,7 +6950,7 @@
           <t>NOVAK Ajda</t>
         </is>
       </c>
-      <c r="U112" t="inlineStr">
+      <c r="X112" t="inlineStr">
         <is>
           <t>39079</t>
         </is>
@@ -6988,7 +7008,7 @@
           <t>DORIA VILARRUBLA Monica</t>
         </is>
       </c>
-      <c r="U113" t="inlineStr">
+      <c r="X113" t="inlineStr">
         <is>
           <t>53051</t>
         </is>
@@ -7046,7 +7066,7 @@
           <t>YAZAWA Aki</t>
         </is>
       </c>
-      <c r="U114" t="inlineStr">
+      <c r="X114" t="inlineStr">
         <is>
           <t>36486</t>
         </is>
@@ -7104,7 +7124,7 @@
           <t>MINTALOVA Eliska</t>
         </is>
       </c>
-      <c r="U115" t="inlineStr">
+      <c r="X115" t="inlineStr">
         <is>
           <t>56169</t>
         </is>
@@ -7162,7 +7182,7 @@
           <t>FABER Anna</t>
         </is>
       </c>
-      <c r="U116" t="inlineStr">
+      <c r="X116" t="inlineStr">
         <is>
           <t>39059</t>
         </is>
@@ -7220,7 +7240,7 @@
           <t>KALISKA Elena</t>
         </is>
       </c>
-      <c r="U117" t="inlineStr">
+      <c r="X117" t="inlineStr">
         <is>
           <t>35366</t>
         </is>
@@ -7278,7 +7298,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U118" t="inlineStr">
+      <c r="X118" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -7336,7 +7356,7 @@
           <t>VOJTOVA Veronika</t>
         </is>
       </c>
-      <c r="U119" t="inlineStr">
+      <c r="X119" t="inlineStr">
         <is>
           <t>35945</t>
         </is>
@@ -7394,7 +7414,7 @@
           <t>WEGMAN Martina</t>
         </is>
       </c>
-      <c r="U120" t="inlineStr">
+      <c r="X120" t="inlineStr">
         <is>
           <t>35345</t>
         </is>
@@ -7452,7 +7472,7 @@
           <t>VALIKOVA Barbora</t>
         </is>
       </c>
-      <c r="U121" t="inlineStr">
+      <c r="X121" t="inlineStr">
         <is>
           <t>37267</t>
         </is>
@@ -7510,7 +7530,7 @@
           <t>LAFONT Marie-Zelia</t>
         </is>
       </c>
-      <c r="U122" t="inlineStr">
+      <c r="X122" t="inlineStr">
         <is>
           <t>35374</t>
         </is>
@@ -7568,7 +7588,7 @@
           <t>ZWOLINSKA Klaudia</t>
         </is>
       </c>
-      <c r="U123" t="inlineStr">
+      <c r="X123" t="inlineStr">
         <is>
           <t>42027</t>
         </is>
@@ -7626,7 +7646,7 @@
           <t>LAWRENCE Rosalyn</t>
         </is>
       </c>
-      <c r="U124" t="inlineStr">
+      <c r="X124" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
@@ -7684,7 +7704,7 @@
           <t>JONES Luuka</t>
         </is>
       </c>
-      <c r="U125" t="inlineStr">
+      <c r="X125" t="inlineStr">
         <is>
           <t>36657</t>
         </is>
@@ -7742,7 +7762,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U126" t="inlineStr">
+      <c r="X126" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -7800,7 +7820,7 @@
           <t>PACIERPNIK Natalia</t>
         </is>
       </c>
-      <c r="U127" t="inlineStr">
+      <c r="X127" t="inlineStr">
         <is>
           <t>35077</t>
         </is>
@@ -7858,7 +7878,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U128" t="inlineStr">
+      <c r="X128" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -7916,7 +7936,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U129" t="inlineStr">
+      <c r="X129" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -7974,7 +7994,7 @@
           <t>KUDEJOVA Katerina</t>
         </is>
       </c>
-      <c r="U130" t="inlineStr">
+      <c r="X130" t="inlineStr">
         <is>
           <t>35034</t>
         </is>
@@ -8032,7 +8052,7 @@
           <t>TERCELJ Eva</t>
         </is>
       </c>
-      <c r="U131" t="inlineStr">
+      <c r="X131" t="inlineStr">
         <is>
           <t>36263</t>
         </is>
@@ -8090,7 +8110,7 @@
           <t>DUKATOVA Jana</t>
         </is>
       </c>
-      <c r="U132" t="inlineStr">
+      <c r="X132" t="inlineStr">
         <is>
           <t>35354</t>
         </is>
@@ -8148,7 +8168,7 @@
           <t>PRIGENT Camille</t>
         </is>
       </c>
-      <c r="U133" t="inlineStr">
+      <c r="X133" t="inlineStr">
         <is>
           <t>41566</t>
         </is>
@@ -8206,7 +8226,7 @@
           <t>KUHNLE Corinna</t>
         </is>
       </c>
-      <c r="U134" t="inlineStr">
+      <c r="X134" t="inlineStr">
         <is>
           <t>35282</t>
         </is>
@@ -8264,7 +8284,7 @@
           <t>CHOURRAUT Maialen</t>
         </is>
       </c>
-      <c r="U135" t="inlineStr">
+      <c r="X135" t="inlineStr">
         <is>
           <t>35787</t>
         </is>
@@ -8322,7 +8342,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U136" t="inlineStr">
+      <c r="X136" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -8380,7 +8400,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U137" t="inlineStr">
+      <c r="X137" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -8438,7 +8458,7 @@
           <t>XU Yongzhao</t>
         </is>
       </c>
-      <c r="U138" t="inlineStr">
+      <c r="X138" t="inlineStr">
         <is>
           <t>69446</t>
         </is>
@@ -8496,7 +8516,7 @@
           <t>ZOU Weijian</t>
         </is>
       </c>
-      <c r="U139" t="inlineStr">
+      <c r="X139" t="inlineStr">
         <is>
           <t>94208</t>
         </is>
@@ -8554,7 +8574,7 @@
           <t>HUANG Fa</t>
         </is>
       </c>
-      <c r="U140" t="inlineStr">
+      <c r="X140" t="inlineStr">
         <is>
           <t>87703</t>
         </is>
@@ -8612,7 +8632,7 @@
           <t>OZOLS Kriss</t>
         </is>
       </c>
-      <c r="U141" t="inlineStr">
+      <c r="X141" t="inlineStr">
         <is>
           <t>48993</t>
         </is>
@@ -8670,7 +8690,7 @@
           <t>YERENGAIPOV Kuanysh</t>
         </is>
       </c>
-      <c r="U142" t="inlineStr">
+      <c r="X142" t="inlineStr">
         <is>
           <t>42085</t>
         </is>
@@ -8728,7 +8748,7 @@
           <t>MIKHAILOV Igor</t>
         </is>
       </c>
-      <c r="U143" t="inlineStr">
+      <c r="X143" t="inlineStr">
         <is>
           <t>44026</t>
         </is>
@@ -8786,7 +8806,7 @@
           <t>CHAKIR Issam</t>
         </is>
       </c>
-      <c r="U144" t="inlineStr">
+      <c r="X144" t="inlineStr">
         <is>
           <t>75631</t>
         </is>
@@ -8897,7 +8917,7 @@
           <t>CARVALHO Jose</t>
         </is>
       </c>
-      <c r="U146" t="inlineStr">
+      <c r="X146" t="inlineStr">
         <is>
           <t>35486</t>
         </is>
@@ -8955,7 +8975,7 @@
           <t>CONEY William</t>
         </is>
       </c>
-      <c r="U147" t="inlineStr">
+      <c r="X147" t="inlineStr">
         <is>
           <t>53138</t>
         </is>
@@ -9013,7 +9033,7 @@
           <t>GIBBONS James</t>
         </is>
       </c>
-      <c r="U148" t="inlineStr">
+      <c r="X148" t="inlineStr">
         <is>
           <t>77314</t>
         </is>
@@ -9071,7 +9091,7 @@
           <t>AMANBAYEV Adil</t>
         </is>
       </c>
-      <c r="U149" t="inlineStr">
+      <c r="X149" t="inlineStr">
         <is>
           <t>68999</t>
         </is>
@@ -9129,7 +9149,7 @@
           <t>SARAMANDIF Terence</t>
         </is>
       </c>
-      <c r="U150" t="inlineStr">
+      <c r="X150" t="inlineStr">
         <is>
           <t>79340</t>
         </is>
@@ -9187,7 +9207,7 @@
           <t>MICOZZI Flavio</t>
         </is>
       </c>
-      <c r="U151" t="inlineStr">
+      <c r="X151" t="inlineStr">
         <is>
           <t>77363</t>
         </is>
@@ -9245,7 +9265,7 @@
           <t>OTTEN Joris</t>
         </is>
       </c>
-      <c r="U152" t="inlineStr">
+      <c r="X152" t="inlineStr">
         <is>
           <t>41698</t>
         </is>
@@ -9303,7 +9323,7 @@
           <t>TANIGUCHI Kazuya</t>
         </is>
       </c>
-      <c r="U153" t="inlineStr">
+      <c r="X153" t="inlineStr">
         <is>
           <t>39699</t>
         </is>
@@ -9361,7 +9381,7 @@
           <t>POTOCNY Marcel</t>
         </is>
       </c>
-      <c r="U154" t="inlineStr">
+      <c r="X154" t="inlineStr">
         <is>
           <t>35235</t>
         </is>
@@ -9419,7 +9439,7 @@
           <t>KULIKOV Alexandr</t>
         </is>
       </c>
-      <c r="U155" t="inlineStr">
+      <c r="X155" t="inlineStr">
         <is>
           <t>39679</t>
         </is>
@@ -9477,7 +9497,7 @@
           <t>WASHER Patrick</t>
         </is>
       </c>
-      <c r="U156" t="inlineStr">
+      <c r="X156" t="inlineStr">
         <is>
           <t>42081</t>
         </is>
@@ -9588,7 +9608,7 @@
           <t>GIBB Benjamin</t>
         </is>
       </c>
-      <c r="U158" t="inlineStr">
+      <c r="X158" t="inlineStr">
         <is>
           <t>36711</t>
         </is>
@@ -9646,7 +9666,7 @@
           <t>LOWTHER Steven</t>
         </is>
       </c>
-      <c r="U159" t="inlineStr">
+      <c r="X159" t="inlineStr">
         <is>
           <t>44811</t>
         </is>
@@ -9704,7 +9724,7 @@
           <t>SASAKI Shota</t>
         </is>
       </c>
-      <c r="U160" t="inlineStr">
+      <c r="X160" t="inlineStr">
         <is>
           <t>41610</t>
         </is>
@@ -9762,7 +9782,7 @@
           <t>NEPOGODIN Aleksandr</t>
         </is>
       </c>
-      <c r="U161" t="inlineStr">
+      <c r="X161" t="inlineStr">
         <is>
           <t>39710</t>
         </is>
@@ -9820,7 +9840,7 @@
           <t>BOURHIS Yves</t>
         </is>
       </c>
-      <c r="U162" t="inlineStr">
+      <c r="X162" t="inlineStr">
         <is>
           <t>63237</t>
         </is>
@@ -9878,7 +9898,7 @@
           <t>SZTUBA Igor</t>
         </is>
       </c>
-      <c r="U163" t="inlineStr">
+      <c r="X163" t="inlineStr">
         <is>
           <t>35087</t>
         </is>
@@ -9936,7 +9956,7 @@
           <t>LOKKEN Zachary</t>
         </is>
       </c>
-      <c r="U164" t="inlineStr">
+      <c r="X164" t="inlineStr">
         <is>
           <t>35069</t>
         </is>
@@ -9994,7 +10014,7 @@
           <t>CECCON Paolo</t>
         </is>
       </c>
-      <c r="U165" t="inlineStr">
+      <c r="X165" t="inlineStr">
         <is>
           <t>39903</t>
         </is>
@@ -10052,7 +10072,7 @@
           <t>BADURA Jergus</t>
         </is>
       </c>
-      <c r="U166" t="inlineStr">
+      <c r="X166" t="inlineStr">
         <is>
           <t>68767</t>
         </is>
@@ -10110,7 +10130,7 @@
           <t>BORROWS Ian</t>
         </is>
       </c>
-      <c r="U167" t="inlineStr">
+      <c r="X167" t="inlineStr">
         <is>
           <t>36534</t>
         </is>
@@ -10168,7 +10188,7 @@
           <t>KOECHLIN Thomas</t>
         </is>
       </c>
-      <c r="U168" t="inlineStr">
+      <c r="X168" t="inlineStr">
         <is>
           <t>35419</t>
         </is>
@@ -10226,7 +10246,7 @@
           <t>JOLY Cedric</t>
         </is>
       </c>
-      <c r="U169" t="inlineStr">
+      <c r="X169" t="inlineStr">
         <is>
           <t>35681</t>
         </is>
@@ -10284,7 +10304,7 @@
           <t>ELOSEGI Ander</t>
         </is>
       </c>
-      <c r="U170" t="inlineStr">
+      <c r="X170" t="inlineStr">
         <is>
           <t>35785</t>
         </is>
@@ -10342,7 +10362,7 @@
           <t>BERCIC Anze</t>
         </is>
       </c>
-      <c r="U171" t="inlineStr">
+      <c r="X171" t="inlineStr">
         <is>
           <t>36253</t>
         </is>
@@ -10400,7 +10420,7 @@
           <t>THOMAS Martin</t>
         </is>
       </c>
-      <c r="U172" t="inlineStr">
+      <c r="X172" t="inlineStr">
         <is>
           <t>35412</t>
         </is>
@@ -10458,7 +10478,7 @@
           <t>MARTIKAN Michal</t>
         </is>
       </c>
-      <c r="U173" t="inlineStr">
+      <c r="X173" t="inlineStr">
         <is>
           <t>35365</t>
         </is>
@@ -10516,7 +10536,7 @@
           <t>NICHOLAS Ella</t>
         </is>
       </c>
-      <c r="U174" t="inlineStr">
+      <c r="X174" t="inlineStr">
         <is>
           <t>36591</t>
         </is>
@@ -10574,7 +10594,7 @@
           <t>SORRIBES Laia</t>
         </is>
       </c>
-      <c r="U175" t="inlineStr">
+      <c r="X175" t="inlineStr">
         <is>
           <t>68822</t>
         </is>
@@ -10632,7 +10652,7 @@
           <t>SAFINA Kamilla</t>
         </is>
       </c>
-      <c r="U176" t="inlineStr">
+      <c r="X176" t="inlineStr">
         <is>
           <t>42095</t>
         </is>
@@ -10690,7 +10710,7 @@
           <t>KUZNETSOVA Daria</t>
         </is>
       </c>
-      <c r="U177" t="inlineStr">
+      <c r="X177" t="inlineStr">
         <is>
           <t>76780</t>
         </is>
@@ -10748,7 +10768,7 @@
           <t>NICHOLAS Jane</t>
         </is>
       </c>
-      <c r="U178" t="inlineStr">
+      <c r="X178" t="inlineStr">
         <is>
           <t>93757</t>
         </is>
@@ -10806,7 +10826,7 @@
           <t>THOMAS Hannah</t>
         </is>
       </c>
-      <c r="U179" t="inlineStr">
+      <c r="X179" t="inlineStr">
         <is>
           <t>85758</t>
         </is>
@@ -10864,7 +10884,7 @@
           <t>LEIBFARTH Evy</t>
         </is>
       </c>
-      <c r="U180" t="inlineStr">
+      <c r="X180" t="inlineStr">
         <is>
           <t>83538</t>
         </is>
@@ -10922,7 +10942,7 @@
           <t>RANDLE Kensa</t>
         </is>
       </c>
-      <c r="U181" t="inlineStr">
+      <c r="X181" t="inlineStr">
         <is>
           <t>51859</t>
         </is>
@@ -10980,7 +11000,7 @@
           <t>BETTERIDGE Lois</t>
         </is>
       </c>
-      <c r="U182" t="inlineStr">
+      <c r="X182" t="inlineStr">
         <is>
           <t>60078</t>
         </is>
@@ -11038,7 +11058,7 @@
           <t>MASLEN Amber</t>
         </is>
       </c>
-      <c r="U183" t="inlineStr">
+      <c r="X183" t="inlineStr">
         <is>
           <t>53074</t>
         </is>
@@ -11096,7 +11116,7 @@
           <t>MALEKOVA Arina</t>
         </is>
       </c>
-      <c r="U184" t="inlineStr">
+      <c r="X184" t="inlineStr">
         <is>
           <t>44024</t>
         </is>
@@ -11154,7 +11174,7 @@
           <t>MALAGUTI Francesca</t>
         </is>
       </c>
-      <c r="U185" t="inlineStr">
+      <c r="X185" t="inlineStr">
         <is>
           <t>77362</t>
         </is>
@@ -11212,7 +11232,7 @@
           <t>BRAENDLE Naemi</t>
         </is>
       </c>
-      <c r="U186" t="inlineStr">
+      <c r="X186" t="inlineStr">
         <is>
           <t>68845</t>
         </is>
@@ -11270,7 +11290,7 @@
           <t>MITASIKOVA Monika</t>
         </is>
       </c>
-      <c r="U187" t="inlineStr">
+      <c r="X187" t="inlineStr">
         <is>
           <t>75445</t>
         </is>
@@ -11328,7 +11348,7 @@
           <t>PELLICER CHICA Laura</t>
         </is>
       </c>
-      <c r="U188" t="inlineStr">
+      <c r="X188" t="inlineStr">
         <is>
           <t>43129</t>
         </is>
@@ -11386,7 +11406,7 @@
           <t>ITO Yoshika</t>
         </is>
       </c>
-      <c r="U189" t="inlineStr">
+      <c r="X189" t="inlineStr">
         <is>
           <t>36647</t>
         </is>
@@ -11444,7 +11464,7 @@
           <t>TAKESHITA Yuriko</t>
         </is>
       </c>
-      <c r="U190" t="inlineStr">
+      <c r="X190" t="inlineStr">
         <is>
           <t>36487</t>
         </is>
@@ -11502,7 +11522,7 @@
           <t>APEL Elena</t>
         </is>
       </c>
-      <c r="U191" t="inlineStr">
+      <c r="X191" t="inlineStr">
         <is>
           <t>51837</t>
         </is>
@@ -11560,7 +11580,7 @@
           <t>LEENDERS Claudia</t>
         </is>
       </c>
-      <c r="U192" t="inlineStr">
+      <c r="X192" t="inlineStr">
         <is>
           <t>35331</t>
         </is>
@@ -11618,7 +11638,7 @@
           <t>HAMER-EVANS Megan</t>
         </is>
       </c>
-      <c r="U193" t="inlineStr">
+      <c r="X193" t="inlineStr">
         <is>
           <t>55138</t>
         </is>
@@ -11676,7 +11696,7 @@
           <t>TEUNISSEN Lena</t>
         </is>
       </c>
-      <c r="U194" t="inlineStr">
+      <c r="X194" t="inlineStr">
         <is>
           <t>35344</t>
         </is>
@@ -11734,7 +11754,7 @@
           <t>FOX Noemie</t>
         </is>
       </c>
-      <c r="U195" t="inlineStr">
+      <c r="X195" t="inlineStr">
         <is>
           <t>44812</t>
         </is>
@@ -11792,7 +11812,7 @@
           <t>NOVAK Ajda</t>
         </is>
       </c>
-      <c r="U196" t="inlineStr">
+      <c r="X196" t="inlineStr">
         <is>
           <t>39079</t>
         </is>
@@ -11850,7 +11870,7 @@
           <t>FABER Anna</t>
         </is>
       </c>
-      <c r="U197" t="inlineStr">
+      <c r="X197" t="inlineStr">
         <is>
           <t>39059</t>
         </is>
@@ -11908,7 +11928,7 @@
           <t>KALISKA Elena</t>
         </is>
       </c>
-      <c r="U198" t="inlineStr">
+      <c r="X198" t="inlineStr">
         <is>
           <t>35366</t>
         </is>
@@ -11966,7 +11986,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U199" t="inlineStr">
+      <c r="X199" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -12024,7 +12044,7 @@
           <t>LAFONT Marie-Zelia</t>
         </is>
       </c>
-      <c r="U200" t="inlineStr">
+      <c r="X200" t="inlineStr">
         <is>
           <t>35374</t>
         </is>
@@ -12082,7 +12102,7 @@
           <t>ZWOLINSKA Klaudia</t>
         </is>
       </c>
-      <c r="U201" t="inlineStr">
+      <c r="X201" t="inlineStr">
         <is>
           <t>42027</t>
         </is>
@@ -12140,7 +12160,7 @@
           <t>LAWRENCE Rosalyn</t>
         </is>
       </c>
-      <c r="U202" t="inlineStr">
+      <c r="X202" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
@@ -12198,7 +12218,7 @@
           <t>JONES Luuka</t>
         </is>
       </c>
-      <c r="U203" t="inlineStr">
+      <c r="X203" t="inlineStr">
         <is>
           <t>36657</t>
         </is>
@@ -12256,7 +12276,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U204" t="inlineStr">
+      <c r="X204" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -12473,7 +12493,7 @@
           <t>ZWOLINSKA Klaudia</t>
         </is>
       </c>
-      <c r="U208" t="inlineStr">
+      <c r="X208" t="inlineStr">
         <is>
           <t>42027</t>
         </is>
@@ -12531,7 +12551,7 @@
           <t>TENG Qianqian</t>
         </is>
       </c>
-      <c r="U209" t="inlineStr">
+      <c r="X209" t="inlineStr">
         <is>
           <t>94209</t>
         </is>
@@ -12589,7 +12609,7 @@
           <t>SCHMID Julia</t>
         </is>
       </c>
-      <c r="U210" t="inlineStr">
+      <c r="X210" t="inlineStr">
         <is>
           <t>85991</t>
         </is>
@@ -12647,7 +12667,7 @@
           <t>YANG Liu</t>
         </is>
       </c>
-      <c r="U211" t="inlineStr">
+      <c r="X211" t="inlineStr">
         <is>
           <t>87649</t>
         </is>
@@ -12705,7 +12725,7 @@
           <t>SAFINA Kamilla</t>
         </is>
       </c>
-      <c r="U212" t="inlineStr">
+      <c r="X212" t="inlineStr">
         <is>
           <t>42095</t>
         </is>
@@ -12763,7 +12783,7 @@
           <t>LEIBFARTH Evy</t>
         </is>
       </c>
-      <c r="U213" t="inlineStr">
+      <c r="X213" t="inlineStr">
         <is>
           <t>83538</t>
         </is>
@@ -12821,7 +12841,7 @@
           <t>THOMAS Hannah</t>
         </is>
       </c>
-      <c r="U214" t="inlineStr">
+      <c r="X214" t="inlineStr">
         <is>
           <t>85758</t>
         </is>
@@ -12879,7 +12899,7 @@
           <t>SATO Ayano</t>
         </is>
       </c>
-      <c r="U215" t="inlineStr">
+      <c r="X215" t="inlineStr">
         <is>
           <t>60374</t>
         </is>
@@ -12937,7 +12957,7 @@
           <t>O'FERRALL Caoimhe</t>
         </is>
       </c>
-      <c r="U216" t="inlineStr">
+      <c r="X216" t="inlineStr">
         <is>
           <t>61007</t>
         </is>
@@ -12995,7 +13015,7 @@
           <t>MISHIMA Ren</t>
         </is>
       </c>
-      <c r="U217" t="inlineStr">
+      <c r="X217" t="inlineStr">
         <is>
           <t>37757</t>
         </is>
@@ -13053,7 +13073,7 @@
           <t>NOVAK Lea</t>
         </is>
       </c>
-      <c r="U218" t="inlineStr">
+      <c r="X218" t="inlineStr">
         <is>
           <t>60323</t>
         </is>
@@ -13111,7 +13131,7 @@
           <t>KOZYREVA Anastasia</t>
         </is>
       </c>
-      <c r="U219" t="inlineStr">
+      <c r="X219" t="inlineStr">
         <is>
           <t>60640</t>
         </is>
@@ -13169,7 +13189,7 @@
           <t>PELLICER CHICA Laura</t>
         </is>
       </c>
-      <c r="U220" t="inlineStr">
+      <c r="X220" t="inlineStr">
         <is>
           <t>43129</t>
         </is>
@@ -13227,7 +13247,7 @@
           <t>BETTERIDGE Lois</t>
         </is>
       </c>
-      <c r="U221" t="inlineStr">
+      <c r="X221" t="inlineStr">
         <is>
           <t>60078</t>
         </is>
@@ -13285,7 +13305,7 @@
           <t>YAGI Airi</t>
         </is>
       </c>
-      <c r="U222" t="inlineStr">
+      <c r="X222" t="inlineStr">
         <is>
           <t>37756</t>
         </is>
@@ -13343,7 +13363,7 @@
           <t>TEUNISSEN Lena</t>
         </is>
       </c>
-      <c r="U223" t="inlineStr">
+      <c r="X223" t="inlineStr">
         <is>
           <t>35344</t>
         </is>
@@ -13401,7 +13421,7 @@
           <t>OGILVIE Sophie</t>
         </is>
       </c>
-      <c r="U224" t="inlineStr">
+      <c r="X224" t="inlineStr">
         <is>
           <t>53134</t>
         </is>
@@ -13459,7 +13479,7 @@
           <t>HOCEVAR Eva Alina</t>
         </is>
       </c>
-      <c r="U225" t="inlineStr">
+      <c r="X225" t="inlineStr">
         <is>
           <t>75533</t>
         </is>
@@ -13517,7 +13537,7 @@
           <t>DOBROTVORSKA Viktoriia</t>
         </is>
       </c>
-      <c r="U226" t="inlineStr">
+      <c r="X226" t="inlineStr">
         <is>
           <t>35526</t>
         </is>
@@ -13575,7 +13595,7 @@
           <t>SABATTINI Chiara</t>
         </is>
       </c>
-      <c r="U227" t="inlineStr">
+      <c r="X227" t="inlineStr">
         <is>
           <t>35219</t>
         </is>
@@ -13633,7 +13653,7 @@
           <t>LUKNAROVA Emanuela</t>
         </is>
       </c>
-      <c r="U228" t="inlineStr">
+      <c r="X228" t="inlineStr">
         <is>
           <t>76973</t>
         </is>
@@ -13691,7 +13711,7 @@
           <t>CHEN Shi</t>
         </is>
       </c>
-      <c r="U229" t="inlineStr">
+      <c r="X229" t="inlineStr">
         <is>
           <t>52027</t>
         </is>
@@ -13749,7 +13769,7 @@
           <t>HAVLICKOVA Katerina</t>
         </is>
       </c>
-      <c r="U230" t="inlineStr">
+      <c r="X230" t="inlineStr">
         <is>
           <t>35048</t>
         </is>
@@ -13807,7 +13827,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U231" t="inlineStr">
+      <c r="X231" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -13865,7 +13885,7 @@
           <t>KOZOROG Alja</t>
         </is>
       </c>
-      <c r="U232" t="inlineStr">
+      <c r="X232" t="inlineStr">
         <is>
           <t>39986</t>
         </is>
@@ -13923,7 +13943,7 @@
           <t>FORROW Bethan</t>
         </is>
       </c>
-      <c r="U233" t="inlineStr">
+      <c r="X233" t="inlineStr">
         <is>
           <t>69065</t>
         </is>
@@ -13981,7 +14001,7 @@
           <t>RIHOVA Eva</t>
         </is>
       </c>
-      <c r="U234" t="inlineStr">
+      <c r="X234" t="inlineStr">
         <is>
           <t>51791</t>
         </is>
@@ -14039,7 +14059,7 @@
           <t>APEL Elena</t>
         </is>
       </c>
-      <c r="U235" t="inlineStr">
+      <c r="X235" t="inlineStr">
         <is>
           <t>51837</t>
         </is>
@@ -14097,7 +14117,7 @@
           <t>SKACHOVA Monika</t>
         </is>
       </c>
-      <c r="U236" t="inlineStr">
+      <c r="X236" t="inlineStr">
         <is>
           <t>53078</t>
         </is>
@@ -14155,7 +14175,7 @@
           <t>GIBSON Eilidh</t>
         </is>
       </c>
-      <c r="U237" t="inlineStr">
+      <c r="X237" t="inlineStr">
         <is>
           <t>36708</t>
         </is>
@@ -14213,7 +14233,7 @@
           <t>DORIA VILARRUBLA Monica</t>
         </is>
       </c>
-      <c r="U238" t="inlineStr">
+      <c r="X238" t="inlineStr">
         <is>
           <t>53051</t>
         </is>
@@ -14271,7 +14291,7 @@
           <t>STANOVSKA Sona</t>
         </is>
       </c>
-      <c r="U239" t="inlineStr">
+      <c r="X239" t="inlineStr">
         <is>
           <t>51647</t>
         </is>
@@ -14329,7 +14349,7 @@
           <t>STOECKLIN Lena</t>
         </is>
       </c>
-      <c r="U240" t="inlineStr">
+      <c r="X240" t="inlineStr">
         <is>
           <t>35822</t>
         </is>
@@ -14387,7 +14407,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U241" t="inlineStr">
+      <c r="X241" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -14445,7 +14465,7 @@
           <t>PRIOUX Lucie</t>
         </is>
       </c>
-      <c r="U242" t="inlineStr">
+      <c r="X242" t="inlineStr">
         <is>
           <t>42984</t>
         </is>
@@ -14503,7 +14523,7 @@
           <t>OLAZABAL Klara</t>
         </is>
       </c>
-      <c r="U243" t="inlineStr">
+      <c r="X243" t="inlineStr">
         <is>
           <t>43985</t>
         </is>
@@ -14561,7 +14581,7 @@
           <t>HERZOG Andrea</t>
         </is>
       </c>
-      <c r="U244" t="inlineStr">
+      <c r="X244" t="inlineStr">
         <is>
           <t>55099</t>
         </is>
@@ -14619,7 +14639,7 @@
           <t>JACQUET Claire</t>
         </is>
       </c>
-      <c r="U245" t="inlineStr">
+      <c r="X245" t="inlineStr">
         <is>
           <t>35684</t>
         </is>
@@ -14677,7 +14697,7 @@
           <t>FOX Noemie</t>
         </is>
       </c>
-      <c r="U246" t="inlineStr">
+      <c r="X246" t="inlineStr">
         <is>
           <t>44812</t>
         </is>
@@ -14735,7 +14755,7 @@
           <t>LAWRENCE Rosalyn</t>
         </is>
       </c>
-      <c r="U247" t="inlineStr">
+      <c r="X247" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
@@ -14793,7 +14813,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U248" t="inlineStr">
+      <c r="X248" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -14851,7 +14871,7 @@
           <t>FISEROVA Tereza</t>
         </is>
       </c>
-      <c r="U249" t="inlineStr">
+      <c r="X249" t="inlineStr">
         <is>
           <t>42016</t>
         </is>
@@ -14909,7 +14929,7 @@
           <t>WERATSCHNIG Nadine</t>
         </is>
       </c>
-      <c r="U250" t="inlineStr">
+      <c r="X250" t="inlineStr">
         <is>
           <t>41613</t>
         </is>
@@ -14967,7 +14987,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U251" t="inlineStr">
+      <c r="X251" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -15025,7 +15045,7 @@
           <t>VILARRUBLA Nuria</t>
         </is>
       </c>
-      <c r="U252" t="inlineStr">
+      <c r="X252" t="inlineStr">
         <is>
           <t>35746</t>
         </is>
@@ -15083,7 +15103,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U253" t="inlineStr">
+      <c r="X253" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -15141,7 +15161,7 @@
           <t>NEPOGODIN Aleksandr</t>
         </is>
       </c>
-      <c r="U254" t="inlineStr">
+      <c r="X254" t="inlineStr">
         <is>
           <t>39710</t>
         </is>
@@ -15199,7 +15219,7 @@
           <t>SANTOS Luca</t>
         </is>
       </c>
-      <c r="U255" t="inlineStr">
+      <c r="X255" t="inlineStr">
         <is>
           <t>69115</t>
         </is>
@@ -15257,7 +15277,7 @@
           <t>SWETNAM Huw</t>
         </is>
       </c>
-      <c r="U256" t="inlineStr">
+      <c r="X256" t="inlineStr">
         <is>
           <t>35652</t>
         </is>
@@ -15315,7 +15335,7 @@
           <t>DESNOS Mathieu</t>
         </is>
       </c>
-      <c r="U257" t="inlineStr">
+      <c r="X257" t="inlineStr">
         <is>
           <t>93791</t>
         </is>
@@ -15373,7 +15393,7 @@
           <t>LEE EDWARDS Ciaran</t>
         </is>
       </c>
-      <c r="U258" t="inlineStr">
+      <c r="X258" t="inlineStr">
         <is>
           <t>35614</t>
         </is>
@@ -15431,7 +15451,7 @@
           <t>HENDRICK Noel</t>
         </is>
       </c>
-      <c r="U259" t="inlineStr">
+      <c r="X259" t="inlineStr">
         <is>
           <t>43003</t>
         </is>
@@ -15489,7 +15509,7 @@
           <t>CHAPPELL Etienne</t>
         </is>
       </c>
-      <c r="U260" t="inlineStr">
+      <c r="X260" t="inlineStr">
         <is>
           <t>75833</t>
         </is>
@@ -15547,7 +15567,7 @@
           <t>FARRELL Oisin</t>
         </is>
       </c>
-      <c r="U261" t="inlineStr">
+      <c r="X261" t="inlineStr">
         <is>
           <t>37916</t>
         </is>
@@ -15605,7 +15625,7 @@
           <t>KANAYA Tohru</t>
         </is>
       </c>
-      <c r="U262" t="inlineStr">
+      <c r="X262" t="inlineStr">
         <is>
           <t>36484</t>
         </is>
@@ -15663,7 +15683,7 @@
           <t>STANOVSKY Samuel</t>
         </is>
       </c>
-      <c r="U263" t="inlineStr">
+      <c r="X263" t="inlineStr">
         <is>
           <t>84121</t>
         </is>
@@ -15721,7 +15741,7 @@
           <t>ALVARENGA Frederico</t>
         </is>
       </c>
-      <c r="U264" t="inlineStr">
+      <c r="X264" t="inlineStr">
         <is>
           <t>71976</t>
         </is>
@@ -15779,7 +15799,7 @@
           <t>KARLSSON Max</t>
         </is>
       </c>
-      <c r="U265" t="inlineStr">
+      <c r="X265" t="inlineStr">
         <is>
           <t>35111</t>
         </is>
@@ -15837,7 +15857,7 @@
           <t>WESTFALL Tyler</t>
         </is>
       </c>
-      <c r="U266" t="inlineStr">
+      <c r="X266" t="inlineStr">
         <is>
           <t>51919</t>
         </is>
@@ -15895,7 +15915,7 @@
           <t>WAHLEN Fredrik</t>
         </is>
       </c>
-      <c r="U267" t="inlineStr">
+      <c r="X267" t="inlineStr">
         <is>
           <t>35102</t>
         </is>
@@ -15953,7 +15973,7 @@
           <t>STANOVSKY Martin</t>
         </is>
       </c>
-      <c r="U268" t="inlineStr">
+      <c r="X268" t="inlineStr">
         <is>
           <t>68782</t>
         </is>
@@ -16011,7 +16031,7 @@
           <t>ROSSI Lucas</t>
         </is>
       </c>
-      <c r="U269" t="inlineStr">
+      <c r="X269" t="inlineStr">
         <is>
           <t>36925</t>
         </is>
@@ -16069,7 +16089,7 @@
           <t>TAYLER Michael</t>
         </is>
       </c>
-      <c r="U270" t="inlineStr">
+      <c r="X270" t="inlineStr">
         <is>
           <t>36262</t>
         </is>
@@ -16127,7 +16147,7 @@
           <t>GHISETTI Davide</t>
         </is>
       </c>
-      <c r="U271" t="inlineStr">
+      <c r="X271" t="inlineStr">
         <is>
           <t>77359</t>
         </is>
@@ -16185,7 +16205,7 @@
           <t>POTOCNY Marcel</t>
         </is>
       </c>
-      <c r="U272" t="inlineStr">
+      <c r="X272" t="inlineStr">
         <is>
           <t>35235</t>
         </is>
@@ -16243,7 +16263,7 @@
           <t>DANGEN Jack</t>
         </is>
       </c>
-      <c r="U273" t="inlineStr">
+      <c r="X273" t="inlineStr">
         <is>
           <t>51865</t>
         </is>
@@ -16301,7 +16321,7 @@
           <t>HAYWARD Ben</t>
         </is>
       </c>
-      <c r="U274" t="inlineStr">
+      <c r="X274" t="inlineStr">
         <is>
           <t>35539</t>
         </is>
@@ -16359,7 +16379,7 @@
           <t>SHABANOV Maxim</t>
         </is>
       </c>
-      <c r="U275" t="inlineStr">
+      <c r="X275" t="inlineStr">
         <is>
           <t>40575</t>
         </is>
@@ -16417,7 +16437,7 @@
           <t>VIANELLO Marco</t>
         </is>
       </c>
-      <c r="U276" t="inlineStr">
+      <c r="X276" t="inlineStr">
         <is>
           <t>54910</t>
         </is>
@@ -16475,7 +16495,7 @@
           <t>MUNSCH Manuel</t>
         </is>
       </c>
-      <c r="U277" t="inlineStr">
+      <c r="X277" t="inlineStr">
         <is>
           <t>35631</t>
         </is>
@@ -16533,7 +16553,7 @@
           <t>DOBY Mathieu</t>
         </is>
       </c>
-      <c r="U278" t="inlineStr">
+      <c r="X278" t="inlineStr">
         <is>
           <t>35292</t>
         </is>
@@ -16591,7 +16611,7 @@
           <t>MAJERCZAK Krzysztof</t>
         </is>
       </c>
-      <c r="U279" t="inlineStr">
+      <c r="X279" t="inlineStr">
         <is>
           <t>53647</t>
         </is>
@@ -16649,7 +16669,7 @@
           <t>BUTCHER Finn</t>
         </is>
       </c>
-      <c r="U280" t="inlineStr">
+      <c r="X280" t="inlineStr">
         <is>
           <t>36663</t>
         </is>
@@ -16707,7 +16727,7 @@
           <t>GILBERT Callum</t>
         </is>
       </c>
-      <c r="U281" t="inlineStr">
+      <c r="X281" t="inlineStr">
         <is>
           <t>42090</t>
         </is>
@@ -16765,7 +16785,7 @@
           <t>YAZAWA Kazuki</t>
         </is>
       </c>
-      <c r="U282" t="inlineStr">
+      <c r="X282" t="inlineStr">
         <is>
           <t>36482</t>
         </is>
@@ -16823,7 +16843,7 @@
           <t>BURGI Quentin</t>
         </is>
       </c>
-      <c r="U283" t="inlineStr">
+      <c r="X283" t="inlineStr">
         <is>
           <t>41590</t>
         </is>
@@ -16881,7 +16901,7 @@
           <t>MAXEINER Tim</t>
         </is>
       </c>
-      <c r="U284" t="inlineStr">
+      <c r="X284" t="inlineStr">
         <is>
           <t>35117</t>
         </is>
@@ -16939,7 +16959,7 @@
           <t>MALEK Andrej</t>
         </is>
       </c>
-      <c r="U285" t="inlineStr">
+      <c r="X285" t="inlineStr">
         <is>
           <t>39246</t>
         </is>
@@ -16997,7 +17017,7 @@
           <t>WEGER Jakob</t>
         </is>
       </c>
-      <c r="U286" t="inlineStr">
+      <c r="X286" t="inlineStr">
         <is>
           <t>54909</t>
         </is>
@@ -17055,7 +17075,7 @@
           <t>TESTEN Niko</t>
         </is>
       </c>
-      <c r="U287" t="inlineStr">
+      <c r="X287" t="inlineStr">
         <is>
           <t>39980</t>
         </is>
@@ -17113,7 +17133,7 @@
           <t>TSVIET Igor</t>
         </is>
       </c>
-      <c r="U288" t="inlineStr">
+      <c r="X288" t="inlineStr">
         <is>
           <t>35527</t>
         </is>
@@ -17171,7 +17191,7 @@
           <t>MADORE Mathurin</t>
         </is>
       </c>
-      <c r="U289" t="inlineStr">
+      <c r="X289" t="inlineStr">
         <is>
           <t>51994</t>
         </is>
@@ -17229,7 +17249,7 @@
           <t>SRABOTNIK Martin</t>
         </is>
       </c>
-      <c r="U290" t="inlineStr">
+      <c r="X290" t="inlineStr">
         <is>
           <t>39080</t>
         </is>
@@ -17287,7 +17307,7 @@
           <t>GONCALVES Pedro</t>
         </is>
       </c>
-      <c r="U291" t="inlineStr">
+      <c r="X291" t="inlineStr">
         <is>
           <t>38017</t>
         </is>
@@ -17345,7 +17365,7 @@
           <t>OHRSTROM Isak</t>
         </is>
       </c>
-      <c r="U292" t="inlineStr">
+      <c r="X292" t="inlineStr">
         <is>
           <t>35101</t>
         </is>
@@ -17403,7 +17423,7 @@
           <t>ADACHI Kazuya</t>
         </is>
       </c>
-      <c r="U293" t="inlineStr">
+      <c r="X293" t="inlineStr">
         <is>
           <t>36646</t>
         </is>
@@ -17461,7 +17481,7 @@
           <t>LAUNAY Antoine</t>
         </is>
       </c>
-      <c r="U294" t="inlineStr">
+      <c r="X294" t="inlineStr">
         <is>
           <t>68776</t>
         </is>
@@ -17519,7 +17539,7 @@
           <t>HALCIN Martin</t>
         </is>
       </c>
-      <c r="U295" t="inlineStr">
+      <c r="X295" t="inlineStr">
         <is>
           <t>35355</t>
         </is>
@@ -17577,7 +17597,7 @@
           <t>ANDERSON Timothy</t>
         </is>
       </c>
-      <c r="U296" t="inlineStr">
+      <c r="X296" t="inlineStr">
         <is>
           <t>38432</t>
         </is>
@@ -17635,7 +17655,7 @@
           <t>HERNANZ Samuel</t>
         </is>
       </c>
-      <c r="U297" t="inlineStr">
+      <c r="X297" t="inlineStr">
         <is>
           <t>35786</t>
         </is>
@@ -17693,7 +17713,7 @@
           <t>SCHWEIKERT Fabian</t>
         </is>
       </c>
-      <c r="U298" t="inlineStr">
+      <c r="X298" t="inlineStr">
         <is>
           <t>38412</t>
         </is>
@@ -17751,7 +17771,7 @@
           <t>LLORENTE David</t>
         </is>
       </c>
-      <c r="U299" t="inlineStr">
+      <c r="X299" t="inlineStr">
         <is>
           <t>51850</t>
         </is>
@@ -17809,7 +17829,7 @@
           <t>WERRO Lukas</t>
         </is>
       </c>
-      <c r="U300" t="inlineStr">
+      <c r="X300" t="inlineStr">
         <is>
           <t>35347</t>
         </is>
@@ -17867,7 +17887,7 @@
           <t>HRADILEK Vavrinec</t>
         </is>
       </c>
-      <c r="U301" t="inlineStr">
+      <c r="X301" t="inlineStr">
         <is>
           <t>35031</t>
         </is>
@@ -17925,7 +17945,7 @@
           <t>PASIUT Michal</t>
         </is>
       </c>
-      <c r="U302" t="inlineStr">
+      <c r="X302" t="inlineStr">
         <is>
           <t>35095</t>
         </is>
@@ -17983,7 +18003,7 @@
           <t>WATKINS Daniel</t>
         </is>
       </c>
-      <c r="U303" t="inlineStr">
+      <c r="X303" t="inlineStr">
         <is>
           <t>38430</t>
         </is>
@@ -18041,7 +18061,7 @@
           <t>CRESPO Joan</t>
         </is>
       </c>
-      <c r="U304" t="inlineStr">
+      <c r="X304" t="inlineStr">
         <is>
           <t>35749</t>
         </is>
@@ -18099,7 +18119,7 @@
           <t>DOUGOUD Martin</t>
         </is>
       </c>
-      <c r="U305" t="inlineStr">
+      <c r="X305" t="inlineStr">
         <is>
           <t>35426</t>
         </is>
@@ -18157,7 +18177,7 @@
           <t>GRIGAR Jakub</t>
         </is>
       </c>
-      <c r="U306" t="inlineStr">
+      <c r="X306" t="inlineStr">
         <is>
           <t>37284</t>
         </is>
@@ -18215,7 +18235,7 @@
           <t>SMOLEN Michal</t>
         </is>
       </c>
-      <c r="U307" t="inlineStr">
+      <c r="X307" t="inlineStr">
         <is>
           <t>36397</t>
         </is>
@@ -18273,7 +18293,7 @@
           <t>POPIELA Dariusz</t>
         </is>
       </c>
-      <c r="U308" t="inlineStr">
+      <c r="X308" t="inlineStr">
         <is>
           <t>35096</t>
         </is>
@@ -18331,7 +18351,7 @@
           <t>DELFOUR Lucien</t>
         </is>
       </c>
-      <c r="U309" t="inlineStr">
+      <c r="X309" t="inlineStr">
         <is>
           <t>36537</t>
         </is>
@@ -18389,7 +18409,7 @@
           <t>NEVEU Boris</t>
         </is>
       </c>
-      <c r="U310" t="inlineStr">
+      <c r="X310" t="inlineStr">
         <is>
           <t>35396</t>
         </is>
@@ -18447,7 +18467,7 @@
           <t>AIGNER Hannes</t>
         </is>
       </c>
-      <c r="U311" t="inlineStr">
+      <c r="X311" t="inlineStr">
         <is>
           <t>35115</t>
         </is>
@@ -18505,7 +18525,7 @@
           <t>PRSKAVEC Jiri</t>
         </is>
       </c>
-      <c r="U312" t="inlineStr">
+      <c r="X312" t="inlineStr">
         <is>
           <t>35033</t>
         </is>
@@ -18563,7 +18583,7 @@
           <t>KAUZER Peter</t>
         </is>
       </c>
-      <c r="U313" t="inlineStr">
+      <c r="X313" t="inlineStr">
         <is>
           <t>35589</t>
         </is>
@@ -18621,7 +18641,7 @@
           <t>PRINDIS Vit</t>
         </is>
       </c>
-      <c r="U314" t="inlineStr">
+      <c r="X314" t="inlineStr">
         <is>
           <t>35065</t>
         </is>
@@ -18679,7 +18699,7 @@
           <t>ZWOLINSKA Klaudia</t>
         </is>
       </c>
-      <c r="U315" t="inlineStr">
+      <c r="X315" t="inlineStr">
         <is>
           <t>42027</t>
         </is>
@@ -18737,7 +18757,7 @@
           <t>TENG Qianqian</t>
         </is>
       </c>
-      <c r="U316" t="inlineStr">
+      <c r="X316" t="inlineStr">
         <is>
           <t>94209</t>
         </is>
@@ -18795,7 +18815,7 @@
           <t>SCHMID Julia</t>
         </is>
       </c>
-      <c r="U317" t="inlineStr">
+      <c r="X317" t="inlineStr">
         <is>
           <t>85991</t>
         </is>
@@ -18853,7 +18873,7 @@
           <t>YANG Liu</t>
         </is>
       </c>
-      <c r="U318" t="inlineStr">
+      <c r="X318" t="inlineStr">
         <is>
           <t>87649</t>
         </is>
@@ -18911,7 +18931,7 @@
           <t>SAFINA Kamilla</t>
         </is>
       </c>
-      <c r="U319" t="inlineStr">
+      <c r="X319" t="inlineStr">
         <is>
           <t>42095</t>
         </is>
@@ -18969,7 +18989,7 @@
           <t>LEIBFARTH Evy</t>
         </is>
       </c>
-      <c r="U320" t="inlineStr">
+      <c r="X320" t="inlineStr">
         <is>
           <t>83538</t>
         </is>
@@ -19027,7 +19047,7 @@
           <t>THOMAS Hannah</t>
         </is>
       </c>
-      <c r="U321" t="inlineStr">
+      <c r="X321" t="inlineStr">
         <is>
           <t>85758</t>
         </is>
@@ -19085,7 +19105,7 @@
           <t>SATO Ayano</t>
         </is>
       </c>
-      <c r="U322" t="inlineStr">
+      <c r="X322" t="inlineStr">
         <is>
           <t>60374</t>
         </is>
@@ -19143,7 +19163,7 @@
           <t>O'FERRALL Caoimhe</t>
         </is>
       </c>
-      <c r="U323" t="inlineStr">
+      <c r="X323" t="inlineStr">
         <is>
           <t>61007</t>
         </is>
@@ -19201,7 +19221,7 @@
           <t>MISHIMA Ren</t>
         </is>
       </c>
-      <c r="U324" t="inlineStr">
+      <c r="X324" t="inlineStr">
         <is>
           <t>37757</t>
         </is>
@@ -19259,7 +19279,7 @@
           <t>NOVAK Lea</t>
         </is>
       </c>
-      <c r="U325" t="inlineStr">
+      <c r="X325" t="inlineStr">
         <is>
           <t>60323</t>
         </is>
@@ -19317,7 +19337,7 @@
           <t>KOZYREVA Anastasia</t>
         </is>
       </c>
-      <c r="U326" t="inlineStr">
+      <c r="X326" t="inlineStr">
         <is>
           <t>60640</t>
         </is>
@@ -19375,7 +19395,7 @@
           <t>PELLICER CHICA Laura</t>
         </is>
       </c>
-      <c r="U327" t="inlineStr">
+      <c r="X327" t="inlineStr">
         <is>
           <t>43129</t>
         </is>
@@ -19433,7 +19453,7 @@
           <t>YAGI Airi</t>
         </is>
       </c>
-      <c r="U328" t="inlineStr">
+      <c r="X328" t="inlineStr">
         <is>
           <t>37756</t>
         </is>
@@ -19491,7 +19511,7 @@
           <t>TEUNISSEN Lena</t>
         </is>
       </c>
-      <c r="U329" t="inlineStr">
+      <c r="X329" t="inlineStr">
         <is>
           <t>35344</t>
         </is>
@@ -19549,7 +19569,7 @@
           <t>SABATTINI Chiara</t>
         </is>
       </c>
-      <c r="U330" t="inlineStr">
+      <c r="X330" t="inlineStr">
         <is>
           <t>35219</t>
         </is>
@@ -19607,7 +19627,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U331" t="inlineStr">
+      <c r="X331" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -19665,7 +19685,7 @@
           <t>KOZOROG Alja</t>
         </is>
       </c>
-      <c r="U332" t="inlineStr">
+      <c r="X332" t="inlineStr">
         <is>
           <t>39986</t>
         </is>
@@ -19723,7 +19743,7 @@
           <t>STOECKLIN Lena</t>
         </is>
       </c>
-      <c r="U333" t="inlineStr">
+      <c r="X333" t="inlineStr">
         <is>
           <t>35822</t>
         </is>
@@ -19781,7 +19801,7 @@
           <t>PRIOUX Lucie</t>
         </is>
       </c>
-      <c r="U334" t="inlineStr">
+      <c r="X334" t="inlineStr">
         <is>
           <t>42984</t>
         </is>
@@ -19839,7 +19859,7 @@
           <t>OLAZABAL Klara</t>
         </is>
       </c>
-      <c r="U335" t="inlineStr">
+      <c r="X335" t="inlineStr">
         <is>
           <t>43985</t>
         </is>
@@ -19897,7 +19917,7 @@
           <t>JACQUET Claire</t>
         </is>
       </c>
-      <c r="U336" t="inlineStr">
+      <c r="X336" t="inlineStr">
         <is>
           <t>35684</t>
         </is>
@@ -19955,7 +19975,7 @@
           <t>FOX Noemie</t>
         </is>
       </c>
-      <c r="U337" t="inlineStr">
+      <c r="X337" t="inlineStr">
         <is>
           <t>44812</t>
         </is>
@@ -20013,7 +20033,7 @@
           <t>LAWRENCE Rosalyn</t>
         </is>
       </c>
-      <c r="U338" t="inlineStr">
+      <c r="X338" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
@@ -20071,7 +20091,7 @@
           <t>WERATSCHNIG Nadine</t>
         </is>
       </c>
-      <c r="U339" t="inlineStr">
+      <c r="X339" t="inlineStr">
         <is>
           <t>41613</t>
         </is>
@@ -20129,7 +20149,7 @@
           <t>VILARRUBLA Nuria</t>
         </is>
       </c>
-      <c r="U340" t="inlineStr">
+      <c r="X340" t="inlineStr">
         <is>
           <t>35746</t>
         </is>
@@ -20187,7 +20207,7 @@
           <t>NEPOGODIN Aleksandr</t>
         </is>
       </c>
-      <c r="U341" t="inlineStr">
+      <c r="X341" t="inlineStr">
         <is>
           <t>39710</t>
         </is>
@@ -20245,7 +20265,7 @@
           <t>SANTOS Luca</t>
         </is>
       </c>
-      <c r="U342" t="inlineStr">
+      <c r="X342" t="inlineStr">
         <is>
           <t>69115</t>
         </is>
@@ -20303,7 +20323,7 @@
           <t>SWETNAM Huw</t>
         </is>
       </c>
-      <c r="U343" t="inlineStr">
+      <c r="X343" t="inlineStr">
         <is>
           <t>35652</t>
         </is>
@@ -20361,7 +20381,7 @@
           <t>CHAPPELL Etienne</t>
         </is>
       </c>
-      <c r="U344" t="inlineStr">
+      <c r="X344" t="inlineStr">
         <is>
           <t>75833</t>
         </is>
@@ -20419,7 +20439,7 @@
           <t>FARRELL Oisin</t>
         </is>
       </c>
-      <c r="U345" t="inlineStr">
+      <c r="X345" t="inlineStr">
         <is>
           <t>37916</t>
         </is>
@@ -20477,7 +20497,7 @@
           <t>KANAYA Tohru</t>
         </is>
       </c>
-      <c r="U346" t="inlineStr">
+      <c r="X346" t="inlineStr">
         <is>
           <t>36484</t>
         </is>
@@ -20535,7 +20555,7 @@
           <t>STANOVSKY Samuel</t>
         </is>
       </c>
-      <c r="U347" t="inlineStr">
+      <c r="X347" t="inlineStr">
         <is>
           <t>84121</t>
         </is>
@@ -20593,7 +20613,7 @@
           <t>ALVARENGA Frederico</t>
         </is>
       </c>
-      <c r="U348" t="inlineStr">
+      <c r="X348" t="inlineStr">
         <is>
           <t>71976</t>
         </is>
@@ -20651,7 +20671,7 @@
           <t>KARLSSON Max</t>
         </is>
       </c>
-      <c r="U349" t="inlineStr">
+      <c r="X349" t="inlineStr">
         <is>
           <t>35111</t>
         </is>
@@ -20709,7 +20729,7 @@
           <t>WESTFALL Tyler</t>
         </is>
       </c>
-      <c r="U350" t="inlineStr">
+      <c r="X350" t="inlineStr">
         <is>
           <t>51919</t>
         </is>
@@ -20767,7 +20787,7 @@
           <t>WAHLEN Fredrik</t>
         </is>
       </c>
-      <c r="U351" t="inlineStr">
+      <c r="X351" t="inlineStr">
         <is>
           <t>35102</t>
         </is>
@@ -20825,7 +20845,7 @@
           <t>STANOVSKY Martin</t>
         </is>
       </c>
-      <c r="U352" t="inlineStr">
+      <c r="X352" t="inlineStr">
         <is>
           <t>68782</t>
         </is>
@@ -20883,7 +20903,7 @@
           <t>ROSSI Lucas</t>
         </is>
       </c>
-      <c r="U353" t="inlineStr">
+      <c r="X353" t="inlineStr">
         <is>
           <t>36925</t>
         </is>
@@ -20941,7 +20961,7 @@
           <t>GHISETTI Davide</t>
         </is>
       </c>
-      <c r="U354" t="inlineStr">
+      <c r="X354" t="inlineStr">
         <is>
           <t>77359</t>
         </is>
@@ -20999,7 +21019,7 @@
           <t>POTOCNY Marcel</t>
         </is>
       </c>
-      <c r="U355" t="inlineStr">
+      <c r="X355" t="inlineStr">
         <is>
           <t>35235</t>
         </is>
@@ -21057,7 +21077,7 @@
           <t>DANGEN Jack</t>
         </is>
       </c>
-      <c r="U356" t="inlineStr">
+      <c r="X356" t="inlineStr">
         <is>
           <t>51865</t>
         </is>
@@ -21115,7 +21135,7 @@
           <t>SHABANOV Maxim</t>
         </is>
       </c>
-      <c r="U357" t="inlineStr">
+      <c r="X357" t="inlineStr">
         <is>
           <t>40575</t>
         </is>
@@ -21173,7 +21193,7 @@
           <t>MAJERCZAK Krzysztof</t>
         </is>
       </c>
-      <c r="U358" t="inlineStr">
+      <c r="X358" t="inlineStr">
         <is>
           <t>53647</t>
         </is>
@@ -21231,7 +21251,7 @@
           <t>GILBERT Callum</t>
         </is>
       </c>
-      <c r="U359" t="inlineStr">
+      <c r="X359" t="inlineStr">
         <is>
           <t>42090</t>
         </is>
@@ -21289,7 +21309,7 @@
           <t>MAXEINER Tim</t>
         </is>
       </c>
-      <c r="U360" t="inlineStr">
+      <c r="X360" t="inlineStr">
         <is>
           <t>35117</t>
         </is>
@@ -21347,7 +21367,7 @@
           <t>WEGER Jakob</t>
         </is>
       </c>
-      <c r="U361" t="inlineStr">
+      <c r="X361" t="inlineStr">
         <is>
           <t>54909</t>
         </is>
@@ -21405,7 +21425,7 @@
           <t>TESTEN Niko</t>
         </is>
       </c>
-      <c r="U362" t="inlineStr">
+      <c r="X362" t="inlineStr">
         <is>
           <t>39980</t>
         </is>
@@ -21463,7 +21483,7 @@
           <t>TSVIET Igor</t>
         </is>
       </c>
-      <c r="U363" t="inlineStr">
+      <c r="X363" t="inlineStr">
         <is>
           <t>35527</t>
         </is>
@@ -21521,7 +21541,7 @@
           <t>SRABOTNIK Martin</t>
         </is>
       </c>
-      <c r="U364" t="inlineStr">
+      <c r="X364" t="inlineStr">
         <is>
           <t>39080</t>
         </is>
@@ -21579,7 +21599,7 @@
           <t>GONCALVES Pedro</t>
         </is>
       </c>
-      <c r="U365" t="inlineStr">
+      <c r="X365" t="inlineStr">
         <is>
           <t>38017</t>
         </is>
@@ -21637,7 +21657,7 @@
           <t>ADACHI Kazuya</t>
         </is>
       </c>
-      <c r="U366" t="inlineStr">
+      <c r="X366" t="inlineStr">
         <is>
           <t>36646</t>
         </is>
@@ -21695,7 +21715,7 @@
           <t>LLORENTE David</t>
         </is>
       </c>
-      <c r="U367" t="inlineStr">
+      <c r="X367" t="inlineStr">
         <is>
           <t>51850</t>
         </is>
@@ -21753,7 +21773,7 @@
           <t>WATKINS Daniel</t>
         </is>
       </c>
-      <c r="U368" t="inlineStr">
+      <c r="X368" t="inlineStr">
         <is>
           <t>38430</t>
         </is>
@@ -21811,7 +21831,7 @@
           <t>CRESPO Joan</t>
         </is>
       </c>
-      <c r="U369" t="inlineStr">
+      <c r="X369" t="inlineStr">
         <is>
           <t>35749</t>
         </is>
@@ -21869,7 +21889,7 @@
           <t>GRIGAR Jakub</t>
         </is>
       </c>
-      <c r="U370" t="inlineStr">
+      <c r="X370" t="inlineStr">
         <is>
           <t>37284</t>
         </is>
@@ -21927,7 +21947,7 @@
           <t>PRINDIS Vit</t>
         </is>
       </c>
-      <c r="U371" t="inlineStr">
+      <c r="X371" t="inlineStr">
         <is>
           <t>35065</t>
         </is>
@@ -22523,7 +22543,7 @@
           <t>SZTUBA Igor</t>
         </is>
       </c>
-      <c r="U383" t="inlineStr">
+      <c r="X383" t="inlineStr">
         <is>
           <t>35087</t>
         </is>
@@ -22581,7 +22601,7 @@
           <t>KOECHLIN Thomas</t>
         </is>
       </c>
-      <c r="U384" t="inlineStr">
+      <c r="X384" t="inlineStr">
         <is>
           <t>35419</t>
         </is>
@@ -22639,7 +22659,7 @@
           <t>ZOU Weijian</t>
         </is>
       </c>
-      <c r="U385" t="inlineStr">
+      <c r="X385" t="inlineStr">
         <is>
           <t>94208</t>
         </is>
@@ -22697,7 +22717,7 @@
           <t>MARTIKAN Michal</t>
         </is>
       </c>
-      <c r="U386" t="inlineStr">
+      <c r="X386" t="inlineStr">
         <is>
           <t>35365</t>
         </is>
@@ -22755,7 +22775,7 @@
           <t>BERCIC Anze</t>
         </is>
       </c>
-      <c r="U387" t="inlineStr">
+      <c r="X387" t="inlineStr">
         <is>
           <t>36253</t>
         </is>
@@ -22813,7 +22833,7 @@
           <t>THOMAS Martin</t>
         </is>
       </c>
-      <c r="U388" t="inlineStr">
+      <c r="X388" t="inlineStr">
         <is>
           <t>35412</t>
         </is>
@@ -22871,7 +22891,7 @@
           <t>NEPOGODIN Aleksandr</t>
         </is>
       </c>
-      <c r="U389" t="inlineStr">
+      <c r="X389" t="inlineStr">
         <is>
           <t>39710</t>
         </is>
@@ -22929,7 +22949,7 @@
           <t>LOKKEN Zachary</t>
         </is>
       </c>
-      <c r="U390" t="inlineStr">
+      <c r="X390" t="inlineStr">
         <is>
           <t>35069</t>
         </is>
@@ -22987,7 +23007,7 @@
           <t>JOLY Cedric</t>
         </is>
       </c>
-      <c r="U391" t="inlineStr">
+      <c r="X391" t="inlineStr">
         <is>
           <t>35681</t>
         </is>
@@ -23045,7 +23065,7 @@
           <t>ELOSEGI Ander</t>
         </is>
       </c>
-      <c r="U392" t="inlineStr">
+      <c r="X392" t="inlineStr">
         <is>
           <t>35785</t>
         </is>
@@ -23103,7 +23123,7 @@
           <t>GARGAUD CHANUT Denis</t>
         </is>
       </c>
-      <c r="U393" t="inlineStr">
+      <c r="X393" t="inlineStr">
         <is>
           <t>35177</t>
         </is>
@@ -23161,7 +23181,7 @@
           <t>ROSSI Sebastian</t>
         </is>
       </c>
-      <c r="U394" t="inlineStr">
+      <c r="X394" t="inlineStr">
         <is>
           <t>36915</t>
         </is>
@@ -23219,7 +23239,7 @@
           <t>BENUS Matej</t>
         </is>
       </c>
-      <c r="U395" t="inlineStr">
+      <c r="X395" t="inlineStr">
         <is>
           <t>35353</t>
         </is>
@@ -23277,7 +23297,7 @@
           <t>HEDWIG Grzegorz</t>
         </is>
       </c>
-      <c r="U396" t="inlineStr">
+      <c r="X396" t="inlineStr">
         <is>
           <t>35465</t>
         </is>
@@ -23335,7 +23355,7 @@
           <t>RAK Tomas</t>
         </is>
       </c>
-      <c r="U397" t="inlineStr">
+      <c r="X397" t="inlineStr">
         <is>
           <t>35056</t>
         </is>
@@ -23393,7 +23413,7 @@
           <t>BOZIC Luka</t>
         </is>
       </c>
-      <c r="U398" t="inlineStr">
+      <c r="X398" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
@@ -23451,7 +23471,7 @@
           <t>ROHAN Lukas</t>
         </is>
       </c>
-      <c r="U399" t="inlineStr">
+      <c r="X399" t="inlineStr">
         <is>
           <t>36114</t>
         </is>
@@ -23509,7 +23529,7 @@
           <t>BOURHIS Jean Pierre</t>
         </is>
       </c>
-      <c r="U400" t="inlineStr">
+      <c r="X400" t="inlineStr">
         <is>
           <t>36968</t>
         </is>
@@ -23567,7 +23587,7 @@
           <t>BORGES Felipe</t>
         </is>
       </c>
-      <c r="U401" t="inlineStr">
+      <c r="X401" t="inlineStr">
         <is>
           <t>38012</t>
         </is>
@@ -23625,7 +23645,7 @@
           <t>SAVSEK Benjamin</t>
         </is>
       </c>
-      <c r="U402" t="inlineStr">
+      <c r="X402" t="inlineStr">
         <is>
           <t>36218</t>
         </is>
@@ -23683,7 +23703,7 @@
           <t>HANEDA Takuya</t>
         </is>
       </c>
-      <c r="U403" t="inlineStr">
+      <c r="X403" t="inlineStr">
         <is>
           <t>36481</t>
         </is>
@@ -23741,7 +23761,7 @@
           <t>ANTON Franz</t>
         </is>
       </c>
-      <c r="U404" t="inlineStr">
+      <c r="X404" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
@@ -23799,7 +23819,7 @@
           <t>EICHFELD Casey</t>
         </is>
       </c>
-      <c r="U405" t="inlineStr">
+      <c r="X405" t="inlineStr">
         <is>
           <t>35067</t>
         </is>
@@ -23857,7 +23877,7 @@
           <t>SHKLIARUK Nikolai</t>
         </is>
       </c>
-      <c r="U406" t="inlineStr">
+      <c r="X406" t="inlineStr">
         <is>
           <t>44025</t>
         </is>
@@ -23915,7 +23935,7 @@
           <t>HEGER Vojtech</t>
         </is>
       </c>
-      <c r="U407" t="inlineStr">
+      <c r="X407" t="inlineStr">
         <is>
           <t>68872</t>
         </is>
@@ -23973,7 +23993,7 @@
           <t>WATKINS Daniel</t>
         </is>
       </c>
-      <c r="U408" t="inlineStr">
+      <c r="X408" t="inlineStr">
         <is>
           <t>38430</t>
         </is>
@@ -24031,7 +24051,7 @@
           <t>ABBOTT Thomas</t>
         </is>
       </c>
-      <c r="U409" t="inlineStr">
+      <c r="X409" t="inlineStr">
         <is>
           <t>36514</t>
         </is>
@@ -24089,7 +24109,7 @@
           <t>TRAVE Miquel</t>
         </is>
       </c>
-      <c r="U410" t="inlineStr">
+      <c r="X410" t="inlineStr">
         <is>
           <t>68998</t>
         </is>
@@ -24147,7 +24167,7 @@
           <t>SZTUBA Kacper</t>
         </is>
       </c>
-      <c r="U411" t="inlineStr">
+      <c r="X411" t="inlineStr">
         <is>
           <t>53636</t>
         </is>
@@ -24205,7 +24225,7 @@
           <t>SLAFKOVSKY Alexander</t>
         </is>
       </c>
-      <c r="U412" t="inlineStr">
+      <c r="X412" t="inlineStr">
         <is>
           <t>35129</t>
         </is>
@@ -24263,7 +24283,7 @@
           <t>LEIBFARTH Evy</t>
         </is>
       </c>
-      <c r="U413" t="inlineStr">
+      <c r="X413" t="inlineStr">
         <is>
           <t>83538</t>
         </is>
@@ -24321,7 +24341,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U414" t="inlineStr">
+      <c r="X414" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -24379,7 +24399,7 @@
           <t>TAKESHITA Yuriko</t>
         </is>
       </c>
-      <c r="U415" t="inlineStr">
+      <c r="X415" t="inlineStr">
         <is>
           <t>36487</t>
         </is>
@@ -24437,7 +24457,7 @@
           <t>SORRIBES Laia</t>
         </is>
       </c>
-      <c r="U416" t="inlineStr">
+      <c r="X416" t="inlineStr">
         <is>
           <t>68822</t>
         </is>
@@ -24495,7 +24515,7 @@
           <t>FOX Noemie</t>
         </is>
       </c>
-      <c r="U417" t="inlineStr">
+      <c r="X417" t="inlineStr">
         <is>
           <t>44812</t>
         </is>
@@ -24553,7 +24573,7 @@
           <t>ZWOLINSKA Klaudia</t>
         </is>
       </c>
-      <c r="U418" t="inlineStr">
+      <c r="X418" t="inlineStr">
         <is>
           <t>42027</t>
         </is>
@@ -24611,7 +24631,7 @@
           <t>HAMER-EVANS Megan</t>
         </is>
       </c>
-      <c r="U419" t="inlineStr">
+      <c r="X419" t="inlineStr">
         <is>
           <t>55138</t>
         </is>
@@ -24669,7 +24689,7 @@
           <t>NOVAK Ajda</t>
         </is>
       </c>
-      <c r="U420" t="inlineStr">
+      <c r="X420" t="inlineStr">
         <is>
           <t>39079</t>
         </is>
@@ -24727,7 +24747,7 @@
           <t>LAFONT Marie-Zelia</t>
         </is>
       </c>
-      <c r="U421" t="inlineStr">
+      <c r="X421" t="inlineStr">
         <is>
           <t>35374</t>
         </is>
@@ -24785,7 +24805,7 @@
           <t>JONES Luuka</t>
         </is>
       </c>
-      <c r="U422" t="inlineStr">
+      <c r="X422" t="inlineStr">
         <is>
           <t>36657</t>
         </is>
@@ -24843,7 +24863,7 @@
           <t>CHOURRAUT Maialen</t>
         </is>
       </c>
-      <c r="U423" t="inlineStr">
+      <c r="X423" t="inlineStr">
         <is>
           <t>35787</t>
         </is>
@@ -24901,7 +24921,7 @@
           <t>YAZAWA Aki</t>
         </is>
       </c>
-      <c r="U424" t="inlineStr">
+      <c r="X424" t="inlineStr">
         <is>
           <t>36486</t>
         </is>
@@ -24959,7 +24979,7 @@
           <t>OGILVIE Sophie</t>
         </is>
       </c>
-      <c r="U425" t="inlineStr">
+      <c r="X425" t="inlineStr">
         <is>
           <t>53134</t>
         </is>
@@ -25017,7 +25037,7 @@
           <t>VALIKOVA Barbora</t>
         </is>
       </c>
-      <c r="U426" t="inlineStr">
+      <c r="X426" t="inlineStr">
         <is>
           <t>37267</t>
         </is>
@@ -25075,7 +25095,7 @@
           <t>PACIERPNIK Natalia</t>
         </is>
       </c>
-      <c r="U427" t="inlineStr">
+      <c r="X427" t="inlineStr">
         <is>
           <t>35077</t>
         </is>
@@ -25133,7 +25153,7 @@
           <t>NEE Ashley</t>
         </is>
       </c>
-      <c r="U428" t="inlineStr">
+      <c r="X428" t="inlineStr">
         <is>
           <t>36363</t>
         </is>
@@ -25191,7 +25211,7 @@
           <t>PRIGENT Camille</t>
         </is>
       </c>
-      <c r="U429" t="inlineStr">
+      <c r="X429" t="inlineStr">
         <is>
           <t>41566</t>
         </is>
@@ -25249,7 +25269,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U430" t="inlineStr">
+      <c r="X430" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -25307,7 +25327,7 @@
           <t>VOJTOVA Veronika</t>
         </is>
       </c>
-      <c r="U431" t="inlineStr">
+      <c r="X431" t="inlineStr">
         <is>
           <t>35945</t>
         </is>
@@ -25365,7 +25385,7 @@
           <t>VILARRUBLA Nuria</t>
         </is>
       </c>
-      <c r="U432" t="inlineStr">
+      <c r="X432" t="inlineStr">
         <is>
           <t>35746</t>
         </is>
@@ -25423,7 +25443,7 @@
           <t>WEGMAN Martina</t>
         </is>
       </c>
-      <c r="U433" t="inlineStr">
+      <c r="X433" t="inlineStr">
         <is>
           <t>35345</t>
         </is>
@@ -25481,7 +25501,7 @@
           <t>DUKATOVA Jana</t>
         </is>
       </c>
-      <c r="U434" t="inlineStr">
+      <c r="X434" t="inlineStr">
         <is>
           <t>35354</t>
         </is>
@@ -25539,7 +25559,7 @@
           <t>KUHNLE Corinna</t>
         </is>
       </c>
-      <c r="U435" t="inlineStr">
+      <c r="X435" t="inlineStr">
         <is>
           <t>35282</t>
         </is>
@@ -25597,7 +25617,7 @@
           <t>DORIA VILARRUBLA Monica</t>
         </is>
       </c>
-      <c r="U436" t="inlineStr">
+      <c r="X436" t="inlineStr">
         <is>
           <t>53051</t>
         </is>
@@ -25655,7 +25675,7 @@
           <t>KUDEJOVA Katerina</t>
         </is>
       </c>
-      <c r="U437" t="inlineStr">
+      <c r="X437" t="inlineStr">
         <is>
           <t>35034</t>
         </is>
@@ -25713,7 +25733,7 @@
           <t>MINTALOVA Eliska</t>
         </is>
       </c>
-      <c r="U438" t="inlineStr">
+      <c r="X438" t="inlineStr">
         <is>
           <t>56169</t>
         </is>
@@ -25771,7 +25791,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U439" t="inlineStr">
+      <c r="X439" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -25829,7 +25849,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U440" t="inlineStr">
+      <c r="X440" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -25887,7 +25907,7 @@
           <t>TERCELJ Eva</t>
         </is>
       </c>
-      <c r="U441" t="inlineStr">
+      <c r="X441" t="inlineStr">
         <is>
           <t>36263</t>
         </is>
@@ -25945,7 +25965,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U442" t="inlineStr">
+      <c r="X442" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -26013,7 +26033,7 @@
           <t>SHKLIARUK Nikolai</t>
         </is>
       </c>
-      <c r="U443" t="inlineStr">
+      <c r="X443" t="inlineStr">
         <is>
           <t>44025</t>
         </is>
@@ -26081,7 +26101,7 @@
           <t>BENUS Matej</t>
         </is>
       </c>
-      <c r="U444" t="inlineStr">
+      <c r="X444" t="inlineStr">
         <is>
           <t>35353</t>
         </is>
@@ -26149,7 +26169,7 @@
           <t>HEGER Vojtech</t>
         </is>
       </c>
-      <c r="U445" t="inlineStr">
+      <c r="X445" t="inlineStr">
         <is>
           <t>68872</t>
         </is>
@@ -26217,7 +26237,7 @@
           <t>MARTIKAN Michal</t>
         </is>
       </c>
-      <c r="U446" t="inlineStr">
+      <c r="X446" t="inlineStr">
         <is>
           <t>35365</t>
         </is>
@@ -26285,7 +26305,7 @@
           <t>ANTON Franz</t>
         </is>
       </c>
-      <c r="U447" t="inlineStr">
+      <c r="X447" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
@@ -26353,7 +26373,7 @@
           <t>EICHFELD Casey</t>
         </is>
       </c>
-      <c r="U448" t="inlineStr">
+      <c r="X448" t="inlineStr">
         <is>
           <t>35067</t>
         </is>
@@ -26421,7 +26441,7 @@
           <t>SAVSEK Benjamin</t>
         </is>
       </c>
-      <c r="U449" t="inlineStr">
+      <c r="X449" t="inlineStr">
         <is>
           <t>36218</t>
         </is>
@@ -26489,7 +26509,7 @@
           <t>SLAFKOVSKY Alexander</t>
         </is>
       </c>
-      <c r="U450" t="inlineStr">
+      <c r="X450" t="inlineStr">
         <is>
           <t>35129</t>
         </is>
@@ -26557,7 +26577,7 @@
           <t>BOZIC Luka</t>
         </is>
       </c>
-      <c r="U451" t="inlineStr">
+      <c r="X451" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
@@ -26625,7 +26645,7 @@
           <t>HEDWIG Grzegorz</t>
         </is>
       </c>
-      <c r="U452" t="inlineStr">
+      <c r="X452" t="inlineStr">
         <is>
           <t>35465</t>
         </is>
@@ -26693,7 +26713,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U453" t="inlineStr">
+      <c r="X453" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -26761,7 +26781,7 @@
           <t>TERCELJ Eva</t>
         </is>
       </c>
-      <c r="U454" t="inlineStr">
+      <c r="X454" t="inlineStr">
         <is>
           <t>36263</t>
         </is>
@@ -26829,7 +26849,7 @@
           <t>VOJTOVA Veronika</t>
         </is>
       </c>
-      <c r="U455" t="inlineStr">
+      <c r="X455" t="inlineStr">
         <is>
           <t>35945</t>
         </is>
@@ -26897,7 +26917,7 @@
           <t>LAFONT Marie-Zelia</t>
         </is>
       </c>
-      <c r="U456" t="inlineStr">
+      <c r="X456" t="inlineStr">
         <is>
           <t>35374</t>
         </is>
@@ -26965,7 +26985,7 @@
           <t>CHOURRAUT Maialen</t>
         </is>
       </c>
-      <c r="U457" t="inlineStr">
+      <c r="X457" t="inlineStr">
         <is>
           <t>35787</t>
         </is>
@@ -27033,7 +27053,7 @@
           <t>JONES Luuka</t>
         </is>
       </c>
-      <c r="U458" t="inlineStr">
+      <c r="X458" t="inlineStr">
         <is>
           <t>36657</t>
         </is>
@@ -27101,7 +27121,7 @@
           <t>LEIBFARTH Evy</t>
         </is>
       </c>
-      <c r="U459" t="inlineStr">
+      <c r="X459" t="inlineStr">
         <is>
           <t>83538</t>
         </is>
@@ -27169,7 +27189,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U460" t="inlineStr">
+      <c r="X460" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -27237,7 +27257,7 @@
           <t>KUHNLE Corinna</t>
         </is>
       </c>
-      <c r="U461" t="inlineStr">
+      <c r="X461" t="inlineStr">
         <is>
           <t>35282</t>
         </is>
@@ -27305,7 +27325,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U462" t="inlineStr">
+      <c r="X462" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -27575,7 +27595,7 @@
           <t>STOECKLIN Lena</t>
         </is>
       </c>
-      <c r="U467" t="inlineStr">
+      <c r="X467" t="inlineStr">
         <is>
           <t>35822</t>
         </is>
@@ -27633,7 +27653,7 @@
           <t>THOMAS Hannah</t>
         </is>
       </c>
-      <c r="U468" t="inlineStr">
+      <c r="X468" t="inlineStr">
         <is>
           <t>85758</t>
         </is>
@@ -27691,7 +27711,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U469" t="inlineStr">
+      <c r="X469" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -27749,7 +27769,7 @@
           <t>JACQUET Claire</t>
         </is>
       </c>
-      <c r="U470" t="inlineStr">
+      <c r="X470" t="inlineStr">
         <is>
           <t>35684</t>
         </is>
@@ -27807,7 +27827,7 @@
           <t>KOZOROG Alja</t>
         </is>
       </c>
-      <c r="U471" t="inlineStr">
+      <c r="X471" t="inlineStr">
         <is>
           <t>39986</t>
         </is>
@@ -27865,7 +27885,7 @@
           <t>SCHMID Julia</t>
         </is>
       </c>
-      <c r="U472" t="inlineStr">
+      <c r="X472" t="inlineStr">
         <is>
           <t>85991</t>
         </is>
@@ -27923,7 +27943,7 @@
           <t>OLAZABAL Klara</t>
         </is>
       </c>
-      <c r="U473" t="inlineStr">
+      <c r="X473" t="inlineStr">
         <is>
           <t>43985</t>
         </is>
@@ -27981,7 +28001,7 @@
           <t>LEIBFARTH Evy</t>
         </is>
       </c>
-      <c r="U474" t="inlineStr">
+      <c r="X474" t="inlineStr">
         <is>
           <t>83538</t>
         </is>
@@ -28039,7 +28059,7 @@
           <t>VILARRUBLA Nuria</t>
         </is>
       </c>
-      <c r="U475" t="inlineStr">
+      <c r="X475" t="inlineStr">
         <is>
           <t>35746</t>
         </is>
@@ -28097,7 +28117,7 @@
           <t>WERATSCHNIG Nadine</t>
         </is>
       </c>
-      <c r="U476" t="inlineStr">
+      <c r="X476" t="inlineStr">
         <is>
           <t>41613</t>
         </is>
@@ -28155,7 +28175,7 @@
           <t>DOBROTVORSKA Viktoriia</t>
         </is>
       </c>
-      <c r="U477" t="inlineStr">
+      <c r="X477" t="inlineStr">
         <is>
           <t>35526</t>
         </is>
@@ -28213,7 +28233,7 @@
           <t>BETTERIDGE Lois</t>
         </is>
       </c>
-      <c r="U478" t="inlineStr">
+      <c r="X478" t="inlineStr">
         <is>
           <t>60078</t>
         </is>
@@ -28271,7 +28291,7 @@
           <t>SKACHOVA Monika</t>
         </is>
       </c>
-      <c r="U479" t="inlineStr">
+      <c r="X479" t="inlineStr">
         <is>
           <t>53078</t>
         </is>
@@ -28329,7 +28349,7 @@
           <t>DORIA VILARRUBLA Monica</t>
         </is>
       </c>
-      <c r="U480" t="inlineStr">
+      <c r="X480" t="inlineStr">
         <is>
           <t>53051</t>
         </is>
@@ -28387,7 +28407,7 @@
           <t>HAVLICKOVA Katerina</t>
         </is>
       </c>
-      <c r="U481" t="inlineStr">
+      <c r="X481" t="inlineStr">
         <is>
           <t>35048</t>
         </is>
@@ -28445,7 +28465,7 @@
           <t>STANOVSKA Sona</t>
         </is>
       </c>
-      <c r="U482" t="inlineStr">
+      <c r="X482" t="inlineStr">
         <is>
           <t>51647</t>
         </is>
@@ -28503,7 +28523,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U483" t="inlineStr">
+      <c r="X483" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -28561,7 +28581,7 @@
           <t>HOCEVAR Eva Alina</t>
         </is>
       </c>
-      <c r="U484" t="inlineStr">
+      <c r="X484" t="inlineStr">
         <is>
           <t>75533</t>
         </is>
@@ -28619,7 +28639,7 @@
           <t>LUKNAROVA Emanuela</t>
         </is>
       </c>
-      <c r="U485" t="inlineStr">
+      <c r="X485" t="inlineStr">
         <is>
           <t>76973</t>
         </is>
@@ -28677,7 +28697,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U486" t="inlineStr">
+      <c r="X486" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -28735,7 +28755,7 @@
           <t>CHEN Shi</t>
         </is>
       </c>
-      <c r="U487" t="inlineStr">
+      <c r="X487" t="inlineStr">
         <is>
           <t>52027</t>
         </is>
@@ -28793,7 +28813,7 @@
           <t>RIHOVA Eva</t>
         </is>
       </c>
-      <c r="U488" t="inlineStr">
+      <c r="X488" t="inlineStr">
         <is>
           <t>51791</t>
         </is>
@@ -28851,7 +28871,7 @@
           <t>HERZOG Andrea</t>
         </is>
       </c>
-      <c r="U489" t="inlineStr">
+      <c r="X489" t="inlineStr">
         <is>
           <t>55099</t>
         </is>
@@ -28909,7 +28929,7 @@
           <t>APEL Elena</t>
         </is>
       </c>
-      <c r="U490" t="inlineStr">
+      <c r="X490" t="inlineStr">
         <is>
           <t>51837</t>
         </is>
@@ -28967,7 +28987,7 @@
           <t>OGILVIE Sophie</t>
         </is>
       </c>
-      <c r="U491" t="inlineStr">
+      <c r="X491" t="inlineStr">
         <is>
           <t>53134</t>
         </is>
@@ -29025,7 +29045,7 @@
           <t>GIBSON Eilidh</t>
         </is>
       </c>
-      <c r="U492" t="inlineStr">
+      <c r="X492" t="inlineStr">
         <is>
           <t>36708</t>
         </is>
@@ -29083,7 +29103,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U493" t="inlineStr">
+      <c r="X493" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -29141,7 +29161,7 @@
           <t>FISEROVA Tereza</t>
         </is>
       </c>
-      <c r="U494" t="inlineStr">
+      <c r="X494" t="inlineStr">
         <is>
           <t>42016</t>
         </is>
@@ -29199,7 +29219,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U495" t="inlineStr">
+      <c r="X495" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -29257,7 +29277,7 @@
           <t>FORROW Bethan</t>
         </is>
       </c>
-      <c r="U496" t="inlineStr">
+      <c r="X496" t="inlineStr">
         <is>
           <t>69065</t>
         </is>
@@ -29315,7 +29335,7 @@
           <t>WAHLEN Fredrik</t>
         </is>
       </c>
-      <c r="U497" t="inlineStr">
+      <c r="X497" t="inlineStr">
         <is>
           <t>35102</t>
         </is>
@@ -29373,7 +29393,7 @@
           <t>POTOCNY Marcel</t>
         </is>
       </c>
-      <c r="U498" t="inlineStr">
+      <c r="X498" t="inlineStr">
         <is>
           <t>35235</t>
         </is>
@@ -29431,7 +29451,7 @@
           <t>CHAPPELL Etienne</t>
         </is>
       </c>
-      <c r="U499" t="inlineStr">
+      <c r="X499" t="inlineStr">
         <is>
           <t>75833</t>
         </is>
@@ -29489,7 +29509,7 @@
           <t>LLORENTE David</t>
         </is>
       </c>
-      <c r="U500" t="inlineStr">
+      <c r="X500" t="inlineStr">
         <is>
           <t>51850</t>
         </is>
@@ -29547,7 +29567,7 @@
           <t>ADACHI Kazuya</t>
         </is>
       </c>
-      <c r="U501" t="inlineStr">
+      <c r="X501" t="inlineStr">
         <is>
           <t>36646</t>
         </is>
@@ -29605,7 +29625,7 @@
           <t>SRABOTNIK Martin</t>
         </is>
       </c>
-      <c r="U502" t="inlineStr">
+      <c r="X502" t="inlineStr">
         <is>
           <t>39080</t>
         </is>
@@ -29663,7 +29683,7 @@
           <t>TESTEN Niko</t>
         </is>
       </c>
-      <c r="U503" t="inlineStr">
+      <c r="X503" t="inlineStr">
         <is>
           <t>39980</t>
         </is>
@@ -29721,7 +29741,7 @@
           <t>PRINDIS Vit</t>
         </is>
       </c>
-      <c r="U504" t="inlineStr">
+      <c r="X504" t="inlineStr">
         <is>
           <t>35065</t>
         </is>
@@ -29779,7 +29799,7 @@
           <t>WATKINS Daniel</t>
         </is>
       </c>
-      <c r="U505" t="inlineStr">
+      <c r="X505" t="inlineStr">
         <is>
           <t>38430</t>
         </is>
@@ -29837,7 +29857,7 @@
           <t>CRESPO Joan</t>
         </is>
       </c>
-      <c r="U506" t="inlineStr">
+      <c r="X506" t="inlineStr">
         <is>
           <t>35749</t>
         </is>
@@ -29895,7 +29915,7 @@
           <t>DOBY Mathieu</t>
         </is>
       </c>
-      <c r="U507" t="inlineStr">
+      <c r="X507" t="inlineStr">
         <is>
           <t>35292</t>
         </is>
@@ -29953,7 +29973,7 @@
           <t>WERRO Lukas</t>
         </is>
       </c>
-      <c r="U508" t="inlineStr">
+      <c r="X508" t="inlineStr">
         <is>
           <t>35347</t>
         </is>
@@ -30011,7 +30031,7 @@
           <t>VIANELLO Marco</t>
         </is>
       </c>
-      <c r="U509" t="inlineStr">
+      <c r="X509" t="inlineStr">
         <is>
           <t>54910</t>
         </is>
@@ -30069,7 +30089,7 @@
           <t>HENDRICK Noel</t>
         </is>
       </c>
-      <c r="U510" t="inlineStr">
+      <c r="X510" t="inlineStr">
         <is>
           <t>43003</t>
         </is>
@@ -30078,7 +30098,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -30093,7 +30113,7 @@
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>Heats</t>
+          <t>Semifinal</t>
         </is>
       </c>
       <c r="F511" t="inlineStr">
@@ -30108,28 +30128,28 @@
       </c>
       <c r="H511" t="inlineStr">
         <is>
-          <t>10:48:00</t>
+          <t>10:48:58</t>
         </is>
       </c>
       <c r="I511" t="inlineStr">
         <is>
-          <t>SLO</t>
+          <t>SWE</t>
         </is>
       </c>
       <c r="J511" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="K511" t="n">
         <v>510</v>
       </c>
       <c r="R511" t="inlineStr">
         <is>
-          <t>KRAGELJ Ursa</t>
-        </is>
-      </c>
-      <c r="U511" t="inlineStr">
-        <is>
-          <t>36264</t>
+          <t>OHRSTROM Isak</t>
+        </is>
+      </c>
+      <c r="X511" t="inlineStr">
+        <is>
+          <t>35101</t>
         </is>
       </c>
     </row>
@@ -30166,28 +30186,28 @@
       </c>
       <c r="H512" t="inlineStr">
         <is>
-          <t>10:48:58</t>
+          <t>10:50:59</t>
         </is>
       </c>
       <c r="I512" t="inlineStr">
         <is>
-          <t>SWE</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="J512" t="n">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="K512" t="n">
         <v>511</v>
       </c>
       <c r="R512" t="inlineStr">
         <is>
-          <t>OHRSTROM Isak</t>
-        </is>
-      </c>
-      <c r="U512" t="inlineStr">
-        <is>
-          <t>35101</t>
+          <t>DESNOS Mathieu</t>
+        </is>
+      </c>
+      <c r="X512" t="inlineStr">
+        <is>
+          <t>93791</t>
         </is>
       </c>
     </row>
@@ -30224,28 +30244,28 @@
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t>10:50:59</t>
+          <t>10:52:59</t>
         </is>
       </c>
       <c r="I513" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>SUI</t>
         </is>
       </c>
       <c r="J513" t="n">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="K513" t="n">
         <v>512</v>
       </c>
       <c r="R513" t="inlineStr">
         <is>
-          <t>DESNOS Mathieu</t>
-        </is>
-      </c>
-      <c r="U513" t="inlineStr">
-        <is>
-          <t>93791</t>
+          <t>MUNSCH Manuel</t>
+        </is>
+      </c>
+      <c r="X513" t="inlineStr">
+        <is>
+          <t>35631</t>
         </is>
       </c>
     </row>
@@ -30282,7 +30302,7 @@
       </c>
       <c r="H514" t="inlineStr">
         <is>
-          <t>10:52:59</t>
+          <t>10:55:00</t>
         </is>
       </c>
       <c r="I514" t="inlineStr">
@@ -30291,19 +30311,19 @@
         </is>
       </c>
       <c r="J514" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="K514" t="n">
         <v>513</v>
       </c>
       <c r="R514" t="inlineStr">
         <is>
-          <t>MUNSCH Manuel</t>
-        </is>
-      </c>
-      <c r="U514" t="inlineStr">
-        <is>
-          <t>35631</t>
+          <t>DOUGOUD Martin</t>
+        </is>
+      </c>
+      <c r="X514" t="inlineStr">
+        <is>
+          <t>35426</t>
         </is>
       </c>
     </row>
@@ -30340,28 +30360,28 @@
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t>10:55:00</t>
+          <t>10:57:00</t>
         </is>
       </c>
       <c r="I515" t="inlineStr">
         <is>
-          <t>SUI</t>
+          <t>GBR</t>
         </is>
       </c>
       <c r="J515" t="n">
-        <v>10</v>
+        <v>57</v>
       </c>
       <c r="K515" t="n">
         <v>514</v>
       </c>
       <c r="R515" t="inlineStr">
         <is>
-          <t>DOUGOUD Martin</t>
-        </is>
-      </c>
-      <c r="U515" t="inlineStr">
-        <is>
-          <t>35426</t>
+          <t>LEE EDWARDS Ciaran</t>
+        </is>
+      </c>
+      <c r="X515" t="inlineStr">
+        <is>
+          <t>35614</t>
         </is>
       </c>
     </row>
@@ -30398,28 +30418,28 @@
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t>10:57:00</t>
+          <t>10:59:00</t>
         </is>
       </c>
       <c r="I516" t="inlineStr">
         <is>
-          <t>GBR</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="J516" t="n">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="K516" t="n">
         <v>515</v>
       </c>
       <c r="R516" t="inlineStr">
         <is>
-          <t>LEE EDWARDS Ciaran</t>
-        </is>
-      </c>
-      <c r="U516" t="inlineStr">
-        <is>
-          <t>35614</t>
+          <t>SMOLEN Michal</t>
+        </is>
+      </c>
+      <c r="X516" t="inlineStr">
+        <is>
+          <t>36397</t>
         </is>
       </c>
     </row>
@@ -30456,28 +30476,28 @@
       </c>
       <c r="H517" t="inlineStr">
         <is>
-          <t>10:59:00</t>
+          <t>11:00:58</t>
         </is>
       </c>
       <c r="I517" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="J517" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="K517" t="n">
         <v>516</v>
       </c>
       <c r="R517" t="inlineStr">
         <is>
-          <t>SMOLEN Michal</t>
-        </is>
-      </c>
-      <c r="U517" t="inlineStr">
-        <is>
-          <t>36397</t>
+          <t>MADORE Mathurin</t>
+        </is>
+      </c>
+      <c r="X517" t="inlineStr">
+        <is>
+          <t>51994</t>
         </is>
       </c>
     </row>
@@ -30514,28 +30534,28 @@
       </c>
       <c r="H518" t="inlineStr">
         <is>
-          <t>11:00:58</t>
+          <t>11:03:00</t>
         </is>
       </c>
       <c r="I518" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="J518" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="K518" t="n">
         <v>517</v>
       </c>
       <c r="R518" t="inlineStr">
         <is>
-          <t>MADORE Mathurin</t>
-        </is>
-      </c>
-      <c r="U518" t="inlineStr">
-        <is>
-          <t>51994</t>
+          <t>TAYLER Michael</t>
+        </is>
+      </c>
+      <c r="X518" t="inlineStr">
+        <is>
+          <t>36262</t>
         </is>
       </c>
     </row>
@@ -30572,28 +30592,28 @@
       </c>
       <c r="H519" t="inlineStr">
         <is>
-          <t>11:03:00</t>
+          <t>11:05:00</t>
         </is>
       </c>
       <c r="I519" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="J519" t="n">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="K519" t="n">
         <v>518</v>
       </c>
       <c r="R519" t="inlineStr">
         <is>
-          <t>TAYLER Michael</t>
-        </is>
-      </c>
-      <c r="U519" t="inlineStr">
-        <is>
-          <t>36262</t>
+          <t>ANDERSON Timothy</t>
+        </is>
+      </c>
+      <c r="X519" t="inlineStr">
+        <is>
+          <t>38432</t>
         </is>
       </c>
     </row>
@@ -30630,28 +30650,28 @@
       </c>
       <c r="H520" t="inlineStr">
         <is>
-          <t>11:05:00</t>
+          <t>11:06:59</t>
         </is>
       </c>
       <c r="I520" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>NZL</t>
         </is>
       </c>
       <c r="J520" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="K520" t="n">
         <v>519</v>
       </c>
       <c r="R520" t="inlineStr">
         <is>
-          <t>ANDERSON Timothy</t>
-        </is>
-      </c>
-      <c r="U520" t="inlineStr">
-        <is>
-          <t>38432</t>
+          <t>BUTCHER Finn</t>
+        </is>
+      </c>
+      <c r="X520" t="inlineStr">
+        <is>
+          <t>36663</t>
         </is>
       </c>
     </row>
@@ -30688,28 +30708,28 @@
       </c>
       <c r="H521" t="inlineStr">
         <is>
-          <t>11:06:59</t>
+          <t>11:09:00</t>
         </is>
       </c>
       <c r="I521" t="inlineStr">
         <is>
-          <t>NZL</t>
+          <t>GER</t>
         </is>
       </c>
       <c r="J521" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="K521" t="n">
         <v>520</v>
       </c>
       <c r="R521" t="inlineStr">
         <is>
-          <t>BUTCHER Finn</t>
-        </is>
-      </c>
-      <c r="U521" t="inlineStr">
-        <is>
-          <t>36663</t>
+          <t>SCHWEIKERT Fabian</t>
+        </is>
+      </c>
+      <c r="X521" t="inlineStr">
+        <is>
+          <t>38412</t>
         </is>
       </c>
     </row>
@@ -30746,28 +30766,28 @@
       </c>
       <c r="H522" t="inlineStr">
         <is>
-          <t>11:09:00</t>
+          <t>11:10:59</t>
         </is>
       </c>
       <c r="I522" t="inlineStr">
         <is>
-          <t>GER</t>
+          <t>JPN</t>
         </is>
       </c>
       <c r="J522" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="K522" t="n">
         <v>521</v>
       </c>
       <c r="R522" t="inlineStr">
         <is>
-          <t>SCHWEIKERT Fabian</t>
-        </is>
-      </c>
-      <c r="U522" t="inlineStr">
-        <is>
-          <t>38412</t>
+          <t>YAZAWA Kazuki</t>
+        </is>
+      </c>
+      <c r="X522" t="inlineStr">
+        <is>
+          <t>36482</t>
         </is>
       </c>
     </row>
@@ -30804,28 +30824,28 @@
       </c>
       <c r="H523" t="inlineStr">
         <is>
-          <t>11:10:59</t>
+          <t>11:12:59</t>
         </is>
       </c>
       <c r="I523" t="inlineStr">
         <is>
-          <t>JPN</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="J523" t="n">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="K523" t="n">
         <v>522</v>
       </c>
       <c r="R523" t="inlineStr">
         <is>
-          <t>YAZAWA Kazuki</t>
-        </is>
-      </c>
-      <c r="U523" t="inlineStr">
-        <is>
-          <t>36482</t>
+          <t>HRADILEK Vavrinec</t>
+        </is>
+      </c>
+      <c r="X523" t="inlineStr">
+        <is>
+          <t>35031</t>
         </is>
       </c>
     </row>
@@ -30862,28 +30882,28 @@
       </c>
       <c r="H524" t="inlineStr">
         <is>
-          <t>11:12:59</t>
+          <t>11:15:00</t>
         </is>
       </c>
       <c r="I524" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="J524" t="n">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="K524" t="n">
         <v>523</v>
       </c>
       <c r="R524" t="inlineStr">
         <is>
-          <t>HRADILEK Vavrinec</t>
-        </is>
-      </c>
-      <c r="U524" t="inlineStr">
-        <is>
-          <t>35031</t>
+          <t>HAYWARD Ben</t>
+        </is>
+      </c>
+      <c r="X524" t="inlineStr">
+        <is>
+          <t>35539</t>
         </is>
       </c>
     </row>
@@ -30920,28 +30940,28 @@
       </c>
       <c r="H525" t="inlineStr">
         <is>
-          <t>11:15:00</t>
+          <t>11:16:59</t>
         </is>
       </c>
       <c r="I525" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>SVK</t>
         </is>
       </c>
       <c r="J525" t="n">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="K525" t="n">
         <v>524</v>
       </c>
       <c r="R525" t="inlineStr">
         <is>
-          <t>HAYWARD Ben</t>
-        </is>
-      </c>
-      <c r="U525" t="inlineStr">
-        <is>
-          <t>35539</t>
+          <t>HALCIN Martin</t>
+        </is>
+      </c>
+      <c r="X525" t="inlineStr">
+        <is>
+          <t>35355</t>
         </is>
       </c>
     </row>
@@ -30978,28 +30998,28 @@
       </c>
       <c r="H526" t="inlineStr">
         <is>
-          <t>11:16:59</t>
+          <t>11:18:58</t>
         </is>
       </c>
       <c r="I526" t="inlineStr">
         <is>
-          <t>SVK</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="J526" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="K526" t="n">
         <v>525</v>
       </c>
       <c r="R526" t="inlineStr">
         <is>
-          <t>HALCIN Martin</t>
-        </is>
-      </c>
-      <c r="U526" t="inlineStr">
-        <is>
-          <t>35355</t>
+          <t>NEVEU Boris</t>
+        </is>
+      </c>
+      <c r="X526" t="inlineStr">
+        <is>
+          <t>35396</t>
         </is>
       </c>
     </row>
@@ -31036,28 +31056,28 @@
       </c>
       <c r="H527" t="inlineStr">
         <is>
-          <t>11:18:58</t>
+          <t>11:20:58</t>
         </is>
       </c>
       <c r="I527" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>SLO</t>
         </is>
       </c>
       <c r="J527" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K527" t="n">
         <v>526</v>
       </c>
       <c r="R527" t="inlineStr">
         <is>
-          <t>NEVEU Boris</t>
-        </is>
-      </c>
-      <c r="U527" t="inlineStr">
-        <is>
-          <t>35396</t>
+          <t>KAUZER Peter</t>
+        </is>
+      </c>
+      <c r="X527" t="inlineStr">
+        <is>
+          <t>35589</t>
         </is>
       </c>
     </row>
@@ -31094,28 +31114,28 @@
       </c>
       <c r="H528" t="inlineStr">
         <is>
-          <t>11:20:58</t>
+          <t>11:23:00</t>
         </is>
       </c>
       <c r="I528" t="inlineStr">
         <is>
-          <t>SLO</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="J528" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="K528" t="n">
         <v>527</v>
       </c>
       <c r="R528" t="inlineStr">
         <is>
-          <t>KAUZER Peter</t>
-        </is>
-      </c>
-      <c r="U528" t="inlineStr">
-        <is>
-          <t>35589</t>
+          <t>HERNANZ Samuel</t>
+        </is>
+      </c>
+      <c r="X528" t="inlineStr">
+        <is>
+          <t>35786</t>
         </is>
       </c>
     </row>
@@ -31152,28 +31172,28 @@
       </c>
       <c r="H529" t="inlineStr">
         <is>
-          <t>11:23:00</t>
+          <t>11:24:58</t>
         </is>
       </c>
       <c r="I529" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="J529" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K529" t="n">
         <v>528</v>
       </c>
       <c r="R529" t="inlineStr">
         <is>
-          <t>HERNANZ Samuel</t>
-        </is>
-      </c>
-      <c r="U529" t="inlineStr">
-        <is>
-          <t>35786</t>
+          <t>PASIUT Michal</t>
+        </is>
+      </c>
+      <c r="X529" t="inlineStr">
+        <is>
+          <t>35095</t>
         </is>
       </c>
     </row>
@@ -31210,28 +31230,28 @@
       </c>
       <c r="H530" t="inlineStr">
         <is>
-          <t>11:24:58</t>
+          <t>11:27:00</t>
         </is>
       </c>
       <c r="I530" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>GER</t>
         </is>
       </c>
       <c r="J530" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="K530" t="n">
         <v>529</v>
       </c>
       <c r="R530" t="inlineStr">
         <is>
-          <t>PASIUT Michal</t>
-        </is>
-      </c>
-      <c r="U530" t="inlineStr">
-        <is>
-          <t>35095</t>
+          <t>AIGNER Hannes</t>
+        </is>
+      </c>
+      <c r="X530" t="inlineStr">
+        <is>
+          <t>35115</t>
         </is>
       </c>
     </row>
@@ -31268,28 +31288,28 @@
       </c>
       <c r="H531" t="inlineStr">
         <is>
-          <t>11:27:00</t>
+          <t>11:29:01</t>
         </is>
       </c>
       <c r="I531" t="inlineStr">
         <is>
-          <t>GER</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="J531" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="K531" t="n">
         <v>530</v>
       </c>
       <c r="R531" t="inlineStr">
         <is>
-          <t>AIGNER Hannes</t>
-        </is>
-      </c>
-      <c r="U531" t="inlineStr">
-        <is>
-          <t>35115</t>
+          <t>LAUNAY Antoine</t>
+        </is>
+      </c>
+      <c r="X531" t="inlineStr">
+        <is>
+          <t>68776</t>
         </is>
       </c>
     </row>
@@ -31326,28 +31346,28 @@
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t>11:29:01</t>
+          <t>11:30:59</t>
         </is>
       </c>
       <c r="I532" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>SVK</t>
         </is>
       </c>
       <c r="J532" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="K532" t="n">
         <v>531</v>
       </c>
       <c r="R532" t="inlineStr">
         <is>
-          <t>LAUNAY Antoine</t>
-        </is>
-      </c>
-      <c r="U532" t="inlineStr">
-        <is>
-          <t>68776</t>
+          <t>MALEK Andrej</t>
+        </is>
+      </c>
+      <c r="X532" t="inlineStr">
+        <is>
+          <t>39246</t>
         </is>
       </c>
     </row>
@@ -31384,28 +31404,28 @@
       </c>
       <c r="H533" t="inlineStr">
         <is>
-          <t>11:30:59</t>
+          <t>11:32:58</t>
         </is>
       </c>
       <c r="I533" t="inlineStr">
         <is>
-          <t>SVK</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="J533" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="K533" t="n">
         <v>532</v>
       </c>
       <c r="R533" t="inlineStr">
         <is>
-          <t>MALEK Andrej</t>
-        </is>
-      </c>
-      <c r="U533" t="inlineStr">
-        <is>
-          <t>39246</t>
+          <t>PRSKAVEC Jiri</t>
+        </is>
+      </c>
+      <c r="X533" t="inlineStr">
+        <is>
+          <t>35033</t>
         </is>
       </c>
     </row>
@@ -31442,28 +31462,28 @@
       </c>
       <c r="H534" t="inlineStr">
         <is>
-          <t>11:32:58</t>
+          <t>11:35:00</t>
         </is>
       </c>
       <c r="I534" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="J534" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K534" t="n">
         <v>533</v>
       </c>
       <c r="R534" t="inlineStr">
         <is>
-          <t>PRSKAVEC Jiri</t>
-        </is>
-      </c>
-      <c r="U534" t="inlineStr">
-        <is>
-          <t>35033</t>
+          <t>POPIELA Dariusz</t>
+        </is>
+      </c>
+      <c r="X534" t="inlineStr">
+        <is>
+          <t>35096</t>
         </is>
       </c>
     </row>
@@ -31500,28 +31520,28 @@
       </c>
       <c r="H535" t="inlineStr">
         <is>
-          <t>11:35:00</t>
+          <t>11:36:58</t>
         </is>
       </c>
       <c r="I535" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="J535" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K535" t="n">
         <v>534</v>
       </c>
       <c r="R535" t="inlineStr">
         <is>
-          <t>POPIELA Dariusz</t>
-        </is>
-      </c>
-      <c r="U535" t="inlineStr">
-        <is>
-          <t>35096</t>
+          <t>DELFOUR Lucien</t>
+        </is>
+      </c>
+      <c r="X535" t="inlineStr">
+        <is>
+          <t>36537</t>
         </is>
       </c>
     </row>
@@ -31558,35 +31578,35 @@
       </c>
       <c r="H536" t="inlineStr">
         <is>
-          <t>11:36:58</t>
+          <t>11:39:00</t>
         </is>
       </c>
       <c r="I536" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="J536" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="K536" t="n">
         <v>535</v>
       </c>
       <c r="R536" t="inlineStr">
         <is>
-          <t>DELFOUR Lucien</t>
-        </is>
-      </c>
-      <c r="U536" t="inlineStr">
-        <is>
-          <t>36537</t>
+          <t>BURGI Quentin</t>
+        </is>
+      </c>
+      <c r="X536" t="inlineStr">
+        <is>
+          <t>41590</t>
         </is>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
@@ -31596,12 +31616,12 @@
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>Semifinal</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="F537" t="inlineStr">
@@ -31616,28 +31636,38 @@
       </c>
       <c r="H537" t="inlineStr">
         <is>
-          <t>11:39:00</t>
+          <t>12:02:59</t>
         </is>
       </c>
       <c r="I537" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>AND</t>
         </is>
       </c>
       <c r="J537" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="K537" t="n">
         <v>536</v>
       </c>
+      <c r="M537" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N537" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="R537" t="inlineStr">
         <is>
-          <t>BURGI Quentin</t>
-        </is>
-      </c>
-      <c r="U537" t="inlineStr">
-        <is>
-          <t>41590</t>
+          <t>DORIA VILARRUBLA Monica</t>
+        </is>
+      </c>
+      <c r="X537" t="inlineStr">
+        <is>
+          <t>53051</t>
         </is>
       </c>
     </row>
@@ -31674,38 +31704,38 @@
       </c>
       <c r="H538" t="inlineStr">
         <is>
-          <t>12:02:59</t>
+          <t>12:05:58</t>
         </is>
       </c>
       <c r="I538" t="inlineStr">
         <is>
-          <t>AND</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="J538" t="n">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="K538" t="n">
         <v>537</v>
       </c>
       <c r="M538" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N538" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R538" t="inlineStr">
         <is>
-          <t>DORIA VILARRUBLA Monica</t>
-        </is>
-      </c>
-      <c r="U538" t="inlineStr">
-        <is>
-          <t>53051</t>
+          <t>LEIBFARTH Evy</t>
+        </is>
+      </c>
+      <c r="X538" t="inlineStr">
+        <is>
+          <t>83538</t>
         </is>
       </c>
     </row>
@@ -31742,38 +31772,38 @@
       </c>
       <c r="H539" t="inlineStr">
         <is>
-          <t>12:05:58</t>
+          <t>12:08:59</t>
         </is>
       </c>
       <c r="I539" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="J539" t="n">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="K539" t="n">
         <v>538</v>
       </c>
       <c r="M539" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N539" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R539" t="inlineStr">
         <is>
-          <t>LEIBFARTH Evy</t>
-        </is>
-      </c>
-      <c r="U539" t="inlineStr">
-        <is>
-          <t>83538</t>
+          <t>JACQUET Claire</t>
+        </is>
+      </c>
+      <c r="X539" t="inlineStr">
+        <is>
+          <t>35684</t>
         </is>
       </c>
     </row>
@@ -31810,38 +31840,38 @@
       </c>
       <c r="H540" t="inlineStr">
         <is>
-          <t>12:08:59</t>
+          <t>12:11:58</t>
         </is>
       </c>
       <c r="I540" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>GBR</t>
         </is>
       </c>
       <c r="J540" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="K540" t="n">
         <v>539</v>
       </c>
       <c r="M540" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N540" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R540" t="inlineStr">
         <is>
-          <t>JACQUET Claire</t>
-        </is>
-      </c>
-      <c r="U540" t="inlineStr">
-        <is>
-          <t>35684</t>
+          <t>OGILVIE Sophie</t>
+        </is>
+      </c>
+      <c r="X540" t="inlineStr">
+        <is>
+          <t>53134</t>
         </is>
       </c>
     </row>
@@ -31878,7 +31908,7 @@
       </c>
       <c r="H541" t="inlineStr">
         <is>
-          <t>12:11:58</t>
+          <t>12:14:59</t>
         </is>
       </c>
       <c r="I541" t="inlineStr">
@@ -31887,29 +31917,29 @@
         </is>
       </c>
       <c r="J541" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="K541" t="n">
         <v>540</v>
       </c>
       <c r="M541" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N541" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R541" t="inlineStr">
         <is>
-          <t>OGILVIE Sophie</t>
-        </is>
-      </c>
-      <c r="U541" t="inlineStr">
-        <is>
-          <t>53134</t>
+          <t>GIBSON Eilidh</t>
+        </is>
+      </c>
+      <c r="X541" t="inlineStr">
+        <is>
+          <t>36708</t>
         </is>
       </c>
     </row>
@@ -31946,38 +31976,38 @@
       </c>
       <c r="H542" t="inlineStr">
         <is>
-          <t>12:14:59</t>
+          <t>12:20:01</t>
         </is>
       </c>
       <c r="I542" t="inlineStr">
         <is>
-          <t>GBR</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="J542" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="K542" t="n">
         <v>541</v>
       </c>
       <c r="M542" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N542" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R542" t="inlineStr">
         <is>
-          <t>GIBSON Eilidh</t>
-        </is>
-      </c>
-      <c r="U542" t="inlineStr">
-        <is>
-          <t>36708</t>
+          <t>SATILA Ana</t>
+        </is>
+      </c>
+      <c r="X542" t="inlineStr">
+        <is>
+          <t>35327</t>
         </is>
       </c>
     </row>
@@ -32014,38 +32044,38 @@
       </c>
       <c r="H543" t="inlineStr">
         <is>
-          <t>12:20:01</t>
+          <t>12:22:58</t>
         </is>
       </c>
       <c r="I543" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>SLO</t>
         </is>
       </c>
       <c r="J543" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="K543" t="n">
         <v>542</v>
       </c>
       <c r="M543" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N543" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R543" t="inlineStr">
         <is>
-          <t>SATILA Ana</t>
-        </is>
-      </c>
-      <c r="U543" t="inlineStr">
-        <is>
-          <t>35327</t>
+          <t>HOCEVAR Eva Alina</t>
+        </is>
+      </c>
+      <c r="X543" t="inlineStr">
+        <is>
+          <t>75533</t>
         </is>
       </c>
     </row>
@@ -32082,38 +32112,38 @@
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t>12:22:58</t>
+          <t>12:25:59</t>
         </is>
       </c>
       <c r="I544" t="inlineStr">
         <is>
-          <t>SLO</t>
+          <t>UKR</t>
         </is>
       </c>
       <c r="J544" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K544" t="n">
         <v>543</v>
       </c>
       <c r="M544" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N544" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R544" t="inlineStr">
         <is>
-          <t>HOCEVAR Eva Alina</t>
-        </is>
-      </c>
-      <c r="U544" t="inlineStr">
-        <is>
-          <t>75533</t>
+          <t>DOBROTVORSKA Viktoriia</t>
+        </is>
+      </c>
+      <c r="X544" t="inlineStr">
+        <is>
+          <t>35526</t>
         </is>
       </c>
     </row>
@@ -32150,38 +32180,38 @@
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t>12:25:59</t>
+          <t>12:28:59</t>
         </is>
       </c>
       <c r="I545" t="inlineStr">
         <is>
-          <t>UKR</t>
+          <t>AUT</t>
         </is>
       </c>
       <c r="J545" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="K545" t="n">
         <v>544</v>
       </c>
       <c r="M545" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N545" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R545" t="inlineStr">
         <is>
-          <t>DOBROTVORSKA Viktoriia</t>
-        </is>
-      </c>
-      <c r="U545" t="inlineStr">
-        <is>
-          <t>35526</t>
+          <t>WOLFFHARDT Viktoria</t>
+        </is>
+      </c>
+      <c r="X545" t="inlineStr">
+        <is>
+          <t>35303</t>
         </is>
       </c>
     </row>
@@ -32218,45 +32248,45 @@
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t>12:28:59</t>
+          <t>12:31:59</t>
         </is>
       </c>
       <c r="I546" t="inlineStr">
         <is>
-          <t>AUT</t>
+          <t>GER</t>
         </is>
       </c>
       <c r="J546" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K546" t="n">
         <v>545</v>
       </c>
       <c r="M546" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N546" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R546" t="inlineStr">
         <is>
-          <t>WOLFFHARDT Viktoria</t>
-        </is>
-      </c>
-      <c r="U546" t="inlineStr">
-        <is>
-          <t>35303</t>
+          <t>HERZOG Andrea</t>
+        </is>
+      </c>
+      <c r="X546" t="inlineStr">
+        <is>
+          <t>55099</t>
         </is>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
@@ -32266,7 +32296,7 @@
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="E547" t="inlineStr">
@@ -32286,38 +32316,38 @@
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t>12:31:59</t>
+          <t>12:39:59</t>
         </is>
       </c>
       <c r="I547" t="inlineStr">
         <is>
-          <t>GER</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="J547" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K547" t="n">
         <v>546</v>
       </c>
       <c r="M547" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N547" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R547" t="inlineStr">
         <is>
-          <t>HERZOG Andrea</t>
-        </is>
-      </c>
-      <c r="U547" t="inlineStr">
-        <is>
-          <t>55099</t>
+          <t>NEVEU Boris</t>
+        </is>
+      </c>
+      <c r="X547" t="inlineStr">
+        <is>
+          <t>35396</t>
         </is>
       </c>
     </row>
@@ -32354,7 +32384,7 @@
       </c>
       <c r="H548" t="inlineStr">
         <is>
-          <t>12:39:59</t>
+          <t>12:42:57</t>
         </is>
       </c>
       <c r="I548" t="inlineStr">
@@ -32363,29 +32393,29 @@
         </is>
       </c>
       <c r="J548" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="K548" t="n">
         <v>547</v>
       </c>
       <c r="M548" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N548" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R548" t="inlineStr">
         <is>
-          <t>NEVEU Boris</t>
-        </is>
-      </c>
-      <c r="U548" t="inlineStr">
-        <is>
-          <t>35396</t>
+          <t>MADORE Mathurin</t>
+        </is>
+      </c>
+      <c r="X548" t="inlineStr">
+        <is>
+          <t>51994</t>
         </is>
       </c>
     </row>
@@ -32422,38 +32452,38 @@
       </c>
       <c r="H549" t="inlineStr">
         <is>
-          <t>12:42:57</t>
+          <t>12:45:58</t>
         </is>
       </c>
       <c r="I549" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>SLO</t>
         </is>
       </c>
       <c r="J549" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="K549" t="n">
         <v>548</v>
       </c>
       <c r="M549" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N549" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R549" t="inlineStr">
         <is>
-          <t>MADORE Mathurin</t>
-        </is>
-      </c>
-      <c r="U549" t="inlineStr">
-        <is>
-          <t>51994</t>
+          <t>KAUZER Peter</t>
+        </is>
+      </c>
+      <c r="X549" t="inlineStr">
+        <is>
+          <t>35589</t>
         </is>
       </c>
     </row>
@@ -32490,38 +32520,38 @@
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t>12:45:58</t>
+          <t>12:48:59</t>
         </is>
       </c>
       <c r="I550" t="inlineStr">
         <is>
-          <t>SLO</t>
+          <t>SVK</t>
         </is>
       </c>
       <c r="J550" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="K550" t="n">
         <v>549</v>
       </c>
       <c r="M550" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N550" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R550" t="inlineStr">
         <is>
-          <t>KAUZER Peter</t>
-        </is>
-      </c>
-      <c r="U550" t="inlineStr">
-        <is>
-          <t>35589</t>
+          <t>HALCIN Martin</t>
+        </is>
+      </c>
+      <c r="X550" t="inlineStr">
+        <is>
+          <t>35355</t>
         </is>
       </c>
     </row>
@@ -32558,38 +32588,38 @@
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t>12:48:59</t>
+          <t>12:51:59</t>
         </is>
       </c>
       <c r="I551" t="inlineStr">
         <is>
-          <t>SVK</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="J551" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="K551" t="n">
         <v>550</v>
       </c>
       <c r="M551" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N551" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R551" t="inlineStr">
         <is>
-          <t>HALCIN Martin</t>
-        </is>
-      </c>
-      <c r="U551" t="inlineStr">
-        <is>
-          <t>35355</t>
+          <t>PRSKAVEC Jiri</t>
+        </is>
+      </c>
+      <c r="X551" t="inlineStr">
+        <is>
+          <t>35033</t>
         </is>
       </c>
     </row>
@@ -32626,38 +32656,38 @@
       </c>
       <c r="H552" t="inlineStr">
         <is>
-          <t>12:51:59</t>
+          <t>12:56:57</t>
         </is>
       </c>
       <c r="I552" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="J552" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="K552" t="n">
         <v>551</v>
       </c>
       <c r="M552" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N552" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R552" t="inlineStr">
         <is>
-          <t>PRSKAVEC Jiri</t>
-        </is>
-      </c>
-      <c r="U552" t="inlineStr">
-        <is>
-          <t>35033</t>
+          <t>PASIUT Michal</t>
+        </is>
+      </c>
+      <c r="X552" t="inlineStr">
+        <is>
+          <t>35095</t>
         </is>
       </c>
     </row>
@@ -32694,38 +32724,38 @@
       </c>
       <c r="H553" t="inlineStr">
         <is>
-          <t>12:56:57</t>
+          <t>12:59:59</t>
         </is>
       </c>
       <c r="I553" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>SVK</t>
         </is>
       </c>
       <c r="J553" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="K553" t="n">
         <v>552</v>
       </c>
       <c r="M553" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N553" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R553" t="inlineStr">
         <is>
-          <t>PASIUT Michal</t>
-        </is>
-      </c>
-      <c r="U553" t="inlineStr">
-        <is>
-          <t>35095</t>
+          <t>MALEK Andrej</t>
+        </is>
+      </c>
+      <c r="X553" t="inlineStr">
+        <is>
+          <t>39246</t>
         </is>
       </c>
     </row>
@@ -32762,38 +32792,38 @@
       </c>
       <c r="H554" t="inlineStr">
         <is>
-          <t>12:59:59</t>
+          <t>13:03:02</t>
         </is>
       </c>
       <c r="I554" t="inlineStr">
         <is>
-          <t>SVK</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="J554" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="K554" t="n">
         <v>553</v>
       </c>
       <c r="M554" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N554" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R554" t="inlineStr">
         <is>
-          <t>MALEK Andrej</t>
-        </is>
-      </c>
-      <c r="U554" t="inlineStr">
-        <is>
-          <t>39246</t>
+          <t>POPIELA Dariusz</t>
+        </is>
+      </c>
+      <c r="X554" t="inlineStr">
+        <is>
+          <t>35096</t>
         </is>
       </c>
     </row>
@@ -32830,38 +32860,38 @@
       </c>
       <c r="H555" t="inlineStr">
         <is>
-          <t>13:03:02</t>
+          <t>13:05:56</t>
         </is>
       </c>
       <c r="I555" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="J555" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K555" t="n">
         <v>554</v>
       </c>
       <c r="M555" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N555" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R555" t="inlineStr">
         <is>
-          <t>POPIELA Dariusz</t>
-        </is>
-      </c>
-      <c r="U555" t="inlineStr">
-        <is>
-          <t>35096</t>
+          <t>PRINDIS Vit</t>
+        </is>
+      </c>
+      <c r="X555" t="inlineStr">
+        <is>
+          <t>35065</t>
         </is>
       </c>
     </row>
@@ -32898,45 +32928,45 @@
       </c>
       <c r="H556" t="inlineStr">
         <is>
-          <t>13:05:56</t>
+          <t>13:09:00</t>
         </is>
       </c>
       <c r="I556" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>GER</t>
         </is>
       </c>
       <c r="J556" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K556" t="n">
         <v>555</v>
       </c>
       <c r="M556" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N556" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R556" t="inlineStr">
         <is>
-          <t>PRINDIS Vit</t>
-        </is>
-      </c>
-      <c r="U556" t="inlineStr">
-        <is>
-          <t>35065</t>
+          <t>AIGNER Hannes</t>
+        </is>
+      </c>
+      <c r="X556" t="inlineStr">
+        <is>
+          <t>35115</t>
         </is>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
@@ -32949,9 +32979,14 @@
           <t>K1</t>
         </is>
       </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>Cross</t>
+        </is>
+      </c>
       <c r="E557" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Forerunner</t>
         </is>
       </c>
       <c r="F557" t="inlineStr">
@@ -32966,45 +33001,30 @@
       </c>
       <c r="H557" t="inlineStr">
         <is>
-          <t>13:09:00</t>
+          <t>13:31:00</t>
         </is>
       </c>
       <c r="I557" t="inlineStr">
         <is>
-          <t>GER</t>
+          <t>SVK</t>
         </is>
       </c>
       <c r="J557" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K557" t="n">
         <v>556</v>
       </c>
-      <c r="M557" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="N557" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="R557" t="inlineStr">
         <is>
-          <t>AIGNER Hannes</t>
-        </is>
-      </c>
-      <c r="U557" t="inlineStr">
-        <is>
-          <t>35115</t>
+          <t>GLEJTEKOVA Simona</t>
         </is>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
@@ -33024,7 +33044,7 @@
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>Forerunner</t>
+          <t>Quarterfinal</t>
         </is>
       </c>
       <c r="F558" t="inlineStr">
@@ -33039,23 +33059,28 @@
       </c>
       <c r="H558" t="inlineStr">
         <is>
-          <t>13:31:00</t>
+          <t>15:03:00</t>
         </is>
       </c>
       <c r="I558" t="inlineStr">
         <is>
-          <t>SVK</t>
+          <t>NED</t>
         </is>
       </c>
       <c r="J558" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K558" t="n">
         <v>557</v>
       </c>
       <c r="R558" t="inlineStr">
         <is>
-          <t>GLEJTEKOVA Simona</t>
+          <t>OTTEN Joris</t>
+        </is>
+      </c>
+      <c r="X558" t="inlineStr">
+        <is>
+          <t>41698</t>
         </is>
       </c>
     </row>
@@ -33102,23 +33127,23 @@
       </c>
       <c r="I559" t="inlineStr">
         <is>
-          <t>NED</t>
+          <t>SVK</t>
         </is>
       </c>
       <c r="J559" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K559" t="n">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="R559" t="inlineStr">
         <is>
-          <t>OTTEN Joris</t>
-        </is>
-      </c>
-      <c r="U559" t="inlineStr">
-        <is>
-          <t>41698</t>
+          <t>RAJNIAK Boris</t>
+        </is>
+      </c>
+      <c r="X559" t="inlineStr">
+        <is>
+          <t>37309</t>
         </is>
       </c>
     </row>
@@ -33165,23 +33190,23 @@
       </c>
       <c r="I560" t="inlineStr">
         <is>
-          <t>SVK</t>
+          <t>SWE</t>
         </is>
       </c>
       <c r="J560" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K560" t="n">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="R560" t="inlineStr">
         <is>
-          <t>RAJNIAK Boris</t>
-        </is>
-      </c>
-      <c r="U560" t="inlineStr">
-        <is>
-          <t>37309</t>
+          <t>WAHLEN Fredrik</t>
+        </is>
+      </c>
+      <c r="X560" t="inlineStr">
+        <is>
+          <t>35102</t>
         </is>
       </c>
     </row>
@@ -33228,23 +33253,23 @@
       </c>
       <c r="I561" t="inlineStr">
         <is>
-          <t>SWE</t>
+          <t>KAZ</t>
         </is>
       </c>
       <c r="J561" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="K561" t="n">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="R561" t="inlineStr">
         <is>
-          <t>WAHLEN Fredrik</t>
-        </is>
-      </c>
-      <c r="U561" t="inlineStr">
-        <is>
-          <t>35102</t>
+          <t>YERENGAIPOV Kuanysh</t>
+        </is>
+      </c>
+      <c r="X561" t="inlineStr">
+        <is>
+          <t>42085</t>
         </is>
       </c>
     </row>
@@ -33276,7 +33301,7 @@
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G562" t="inlineStr">
@@ -33286,28 +33311,28 @@
       </c>
       <c r="H562" t="inlineStr">
         <is>
-          <t>15:03:00</t>
+          <t>15:07:30</t>
         </is>
       </c>
       <c r="I562" t="inlineStr">
         <is>
-          <t>KAZ</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="J562" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="K562" t="n">
         <v>558</v>
       </c>
       <c r="R562" t="inlineStr">
         <is>
-          <t>YERENGAIPOV Kuanysh</t>
-        </is>
-      </c>
-      <c r="U562" t="inlineStr">
-        <is>
-          <t>42085</t>
+          <t>GONCALVES Pedro</t>
+        </is>
+      </c>
+      <c r="X562" t="inlineStr">
+        <is>
+          <t>38017</t>
         </is>
       </c>
     </row>
@@ -33354,23 +33379,23 @@
       </c>
       <c r="I563" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>RUS</t>
         </is>
       </c>
       <c r="J563" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="K563" t="n">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="R563" t="inlineStr">
         <is>
-          <t>GONCALVES Pedro</t>
-        </is>
-      </c>
-      <c r="U563" t="inlineStr">
-        <is>
-          <t>38017</t>
+          <t>SHABANOV Maxim</t>
+        </is>
+      </c>
+      <c r="X563" t="inlineStr">
+        <is>
+          <t>40575</t>
         </is>
       </c>
     </row>
@@ -33417,23 +33442,23 @@
       </c>
       <c r="I564" t="inlineStr">
         <is>
-          <t>RUS</t>
+          <t>KAZ</t>
         </is>
       </c>
       <c r="J564" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="K564" t="n">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="R564" t="inlineStr">
         <is>
-          <t>SHABANOV Maxim</t>
-        </is>
-      </c>
-      <c r="U564" t="inlineStr">
-        <is>
-          <t>40575</t>
+          <t>STANOVSKY Martin</t>
+        </is>
+      </c>
+      <c r="X564" t="inlineStr">
+        <is>
+          <t>68782</t>
         </is>
       </c>
     </row>
@@ -33480,23 +33505,23 @@
       </c>
       <c r="I565" t="inlineStr">
         <is>
-          <t>KAZ</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="J565" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K565" t="n">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="R565" t="inlineStr">
         <is>
-          <t>STANOVSKY Martin</t>
-        </is>
-      </c>
-      <c r="U565" t="inlineStr">
-        <is>
-          <t>68782</t>
+          <t>WOS Michal</t>
+        </is>
+      </c>
+      <c r="X565" t="inlineStr">
+        <is>
+          <t>65063</t>
         </is>
       </c>
     </row>
@@ -33528,7 +33553,7 @@
       </c>
       <c r="F566" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G566" t="inlineStr">
@@ -33538,28 +33563,28 @@
       </c>
       <c r="H566" t="inlineStr">
         <is>
-          <t>15:07:30</t>
+          <t>15:12:00</t>
         </is>
       </c>
       <c r="I566" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>GBR</t>
         </is>
       </c>
       <c r="J566" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K566" t="n">
         <v>559</v>
       </c>
       <c r="R566" t="inlineStr">
         <is>
-          <t>WOS Michal</t>
-        </is>
-      </c>
-      <c r="U566" t="inlineStr">
-        <is>
-          <t>65063</t>
+          <t>CHAPPELL Etienne</t>
+        </is>
+      </c>
+      <c r="X566" t="inlineStr">
+        <is>
+          <t>75833</t>
         </is>
       </c>
     </row>
@@ -33606,23 +33631,23 @@
       </c>
       <c r="I567" t="inlineStr">
         <is>
-          <t>GBR</t>
+          <t>RUS</t>
         </is>
       </c>
       <c r="J567" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K567" t="n">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="R567" t="inlineStr">
         <is>
-          <t>CHAPPELL Etienne</t>
-        </is>
-      </c>
-      <c r="U567" t="inlineStr">
-        <is>
-          <t>75833</t>
+          <t>NEPOGODIN Aleksandr</t>
+        </is>
+      </c>
+      <c r="X567" t="inlineStr">
+        <is>
+          <t>39710</t>
         </is>
       </c>
     </row>
@@ -33669,23 +33694,23 @@
       </c>
       <c r="I568" t="inlineStr">
         <is>
-          <t>RUS</t>
+          <t>MRI</t>
         </is>
       </c>
       <c r="J568" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="K568" t="n">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="R568" t="inlineStr">
         <is>
-          <t>NEPOGODIN Aleksandr</t>
-        </is>
-      </c>
-      <c r="U568" t="inlineStr">
-        <is>
-          <t>39710</t>
+          <t>SARAMANDIF Terence</t>
+        </is>
+      </c>
+      <c r="X568" t="inlineStr">
+        <is>
+          <t>79340</t>
         </is>
       </c>
     </row>
@@ -33732,23 +33757,23 @@
       </c>
       <c r="I569" t="inlineStr">
         <is>
-          <t>MRI</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="J569" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K569" t="n">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="R569" t="inlineStr">
         <is>
-          <t>SARAMANDIF Terence</t>
-        </is>
-      </c>
-      <c r="U569" t="inlineStr">
-        <is>
-          <t>79340</t>
+          <t>ZAZIABLO Jaroslaw</t>
+        </is>
+      </c>
+      <c r="X569" t="inlineStr">
+        <is>
+          <t>75728</t>
         </is>
       </c>
     </row>
@@ -33780,7 +33805,7 @@
       </c>
       <c r="F570" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G570" t="inlineStr">
@@ -33790,28 +33815,28 @@
       </c>
       <c r="H570" t="inlineStr">
         <is>
-          <t>15:12:00</t>
+          <t>15:16:30</t>
         </is>
       </c>
       <c r="I570" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>IRL</t>
         </is>
       </c>
       <c r="J570" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K570" t="n">
         <v>560</v>
       </c>
       <c r="R570" t="inlineStr">
         <is>
-          <t>ZAZIABLO Jaroslaw</t>
-        </is>
-      </c>
-      <c r="U570" t="inlineStr">
-        <is>
-          <t>75728</t>
+          <t>FARRELL Oisin</t>
+        </is>
+      </c>
+      <c r="X570" t="inlineStr">
+        <is>
+          <t>37916</t>
         </is>
       </c>
     </row>
@@ -33858,23 +33883,23 @@
       </c>
       <c r="I571" t="inlineStr">
         <is>
-          <t>IRL</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="J571" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="K571" t="n">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="R571" t="inlineStr">
         <is>
-          <t>FARRELL Oisin</t>
-        </is>
-      </c>
-      <c r="U571" t="inlineStr">
-        <is>
-          <t>37916</t>
+          <t>HRADILEK Vavrinec</t>
+        </is>
+      </c>
+      <c r="X571" t="inlineStr">
+        <is>
+          <t>35031</t>
         </is>
       </c>
     </row>
@@ -33921,23 +33946,23 @@
       </c>
       <c r="I572" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>SWE</t>
         </is>
       </c>
       <c r="J572" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K572" t="n">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="R572" t="inlineStr">
         <is>
-          <t>HRADILEK Vavrinec</t>
-        </is>
-      </c>
-      <c r="U572" t="inlineStr">
-        <is>
-          <t>35031</t>
+          <t>KARLSSON Max</t>
+        </is>
+      </c>
+      <c r="X572" t="inlineStr">
+        <is>
+          <t>35111</t>
         </is>
       </c>
     </row>
@@ -33984,30 +34009,30 @@
       </c>
       <c r="I573" t="inlineStr">
         <is>
-          <t>SWE</t>
+          <t>LAT</t>
         </is>
       </c>
       <c r="J573" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="K573" t="n">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="R573" t="inlineStr">
         <is>
-          <t>KARLSSON Max</t>
-        </is>
-      </c>
-      <c r="U573" t="inlineStr">
-        <is>
-          <t>35111</t>
+          <t>STANOVSKY Samuel</t>
+        </is>
+      </c>
+      <c r="X573" t="inlineStr">
+        <is>
+          <t>84121</t>
         </is>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
@@ -34027,12 +34052,12 @@
       </c>
       <c r="E574" t="inlineStr">
         <is>
-          <t>Quarterfinal</t>
+          <t>Semifinal</t>
         </is>
       </c>
       <c r="F574" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G574" t="inlineStr">
@@ -34042,28 +34067,28 @@
       </c>
       <c r="H574" t="inlineStr">
         <is>
-          <t>15:16:30</t>
+          <t>15:21:00</t>
         </is>
       </c>
       <c r="I574" t="inlineStr">
         <is>
-          <t>LAT</t>
+          <t>SVK</t>
         </is>
       </c>
       <c r="J574" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="K574" t="n">
         <v>561</v>
       </c>
       <c r="R574" t="inlineStr">
         <is>
-          <t>STANOVSKY Samuel</t>
-        </is>
-      </c>
-      <c r="U574" t="inlineStr">
-        <is>
-          <t>84121</t>
+          <t>BALEJOVA Suzana</t>
+        </is>
+      </c>
+      <c r="X574" t="inlineStr">
+        <is>
+          <t>97411</t>
         </is>
       </c>
     </row>
@@ -34110,23 +34135,23 @@
       </c>
       <c r="I575" t="inlineStr">
         <is>
-          <t>SVK</t>
+          <t>RUS</t>
         </is>
       </c>
       <c r="J575" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K575" t="n">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="R575" t="inlineStr">
         <is>
-          <t>BALEJOVA Suzana</t>
-        </is>
-      </c>
-      <c r="U575" t="inlineStr">
-        <is>
-          <t>97411</t>
+          <t>KUZNETSOVA Daria</t>
+        </is>
+      </c>
+      <c r="X575" t="inlineStr">
+        <is>
+          <t>76780</t>
         </is>
       </c>
     </row>
@@ -34158,7 +34183,7 @@
       </c>
       <c r="F576" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G576" t="inlineStr">
@@ -34168,28 +34193,28 @@
       </c>
       <c r="H576" t="inlineStr">
         <is>
-          <t>15:21:00</t>
+          <t>15:25:30</t>
         </is>
       </c>
       <c r="I576" t="inlineStr">
         <is>
-          <t>RUS</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="J576" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K576" t="n">
         <v>562</v>
       </c>
       <c r="R576" t="inlineStr">
         <is>
-          <t>KUZNETSOVA Daria</t>
-        </is>
-      </c>
-      <c r="U576" t="inlineStr">
-        <is>
-          <t>76780</t>
+          <t>LEIBFARTH Evy</t>
+        </is>
+      </c>
+      <c r="X576" t="inlineStr">
+        <is>
+          <t>83538</t>
         </is>
       </c>
     </row>
@@ -34240,26 +34265,26 @@
         </is>
       </c>
       <c r="J577" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K577" t="n">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="R577" t="inlineStr">
         <is>
-          <t>LEIBFARTH Evy</t>
-        </is>
-      </c>
-      <c r="U577" t="inlineStr">
-        <is>
-          <t>83538</t>
+          <t>NEE Ashley</t>
+        </is>
+      </c>
+      <c r="X577" t="inlineStr">
+        <is>
+          <t>36363</t>
         </is>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
@@ -34284,7 +34309,7 @@
       </c>
       <c r="F578" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G578" t="inlineStr">
@@ -34294,28 +34319,28 @@
       </c>
       <c r="H578" t="inlineStr">
         <is>
-          <t>15:25:30</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="I578" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="J578" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K578" t="n">
         <v>563</v>
       </c>
       <c r="R578" t="inlineStr">
         <is>
-          <t>NEE Ashley</t>
-        </is>
-      </c>
-      <c r="U578" t="inlineStr">
-        <is>
-          <t>36363</t>
+          <t>GONCALVES Pedro</t>
+        </is>
+      </c>
+      <c r="X578" t="inlineStr">
+        <is>
+          <t>38017</t>
         </is>
       </c>
     </row>
@@ -34362,23 +34387,23 @@
       </c>
       <c r="I579" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>SVK</t>
         </is>
       </c>
       <c r="J579" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K579" t="n">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="R579" t="inlineStr">
         <is>
-          <t>GONCALVES Pedro</t>
-        </is>
-      </c>
-      <c r="U579" t="inlineStr">
-        <is>
-          <t>38017</t>
+          <t>RAJNIAK Boris</t>
+        </is>
+      </c>
+      <c r="X579" t="inlineStr">
+        <is>
+          <t>37309</t>
         </is>
       </c>
     </row>
@@ -34425,23 +34450,23 @@
       </c>
       <c r="I580" t="inlineStr">
         <is>
-          <t>SVK</t>
+          <t>KAZ</t>
         </is>
       </c>
       <c r="J580" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K580" t="n">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="R580" t="inlineStr">
         <is>
-          <t>RAJNIAK Boris</t>
-        </is>
-      </c>
-      <c r="U580" t="inlineStr">
-        <is>
-          <t>37309</t>
+          <t>STANOVSKY Martin</t>
+        </is>
+      </c>
+      <c r="X580" t="inlineStr">
+        <is>
+          <t>68782</t>
         </is>
       </c>
     </row>
@@ -34492,19 +34517,19 @@
         </is>
       </c>
       <c r="J581" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="K581" t="n">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="R581" t="inlineStr">
         <is>
-          <t>STANOVSKY Martin</t>
-        </is>
-      </c>
-      <c r="U581" t="inlineStr">
-        <is>
-          <t>68782</t>
+          <t>YERENGAIPOV Kuanysh</t>
+        </is>
+      </c>
+      <c r="X581" t="inlineStr">
+        <is>
+          <t>42085</t>
         </is>
       </c>
     </row>
@@ -34536,7 +34561,7 @@
       </c>
       <c r="F582" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G582" t="inlineStr">
@@ -34546,28 +34571,28 @@
       </c>
       <c r="H582" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:34:30</t>
         </is>
       </c>
       <c r="I582" t="inlineStr">
         <is>
-          <t>KAZ</t>
+          <t>GBR</t>
         </is>
       </c>
       <c r="J582" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="K582" t="n">
         <v>564</v>
       </c>
       <c r="R582" t="inlineStr">
         <is>
-          <t>YERENGAIPOV Kuanysh</t>
-        </is>
-      </c>
-      <c r="U582" t="inlineStr">
-        <is>
-          <t>42085</t>
+          <t>CHAPPELL Etienne</t>
+        </is>
+      </c>
+      <c r="X582" t="inlineStr">
+        <is>
+          <t>75833</t>
         </is>
       </c>
     </row>
@@ -34614,23 +34639,23 @@
       </c>
       <c r="I583" t="inlineStr">
         <is>
-          <t>GBR</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="J583" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K583" t="n">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="R583" t="inlineStr">
         <is>
-          <t>CHAPPELL Etienne</t>
-        </is>
-      </c>
-      <c r="U583" t="inlineStr">
-        <is>
-          <t>75833</t>
+          <t>HRADILEK Vavrinec</t>
+        </is>
+      </c>
+      <c r="X583" t="inlineStr">
+        <is>
+          <t>35031</t>
         </is>
       </c>
     </row>
@@ -34677,23 +34702,23 @@
       </c>
       <c r="I584" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>SWE</t>
         </is>
       </c>
       <c r="J584" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K584" t="n">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="R584" t="inlineStr">
         <is>
-          <t>HRADILEK Vavrinec</t>
-        </is>
-      </c>
-      <c r="U584" t="inlineStr">
-        <is>
-          <t>35031</t>
+          <t>KARLSSON Max</t>
+        </is>
+      </c>
+      <c r="X584" t="inlineStr">
+        <is>
+          <t>35111</t>
         </is>
       </c>
     </row>
@@ -34740,30 +34765,30 @@
       </c>
       <c r="I585" t="inlineStr">
         <is>
-          <t>SWE</t>
+          <t>RUS</t>
         </is>
       </c>
       <c r="J585" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K585" t="n">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="R585" t="inlineStr">
         <is>
-          <t>KARLSSON Max</t>
-        </is>
-      </c>
-      <c r="U585" t="inlineStr">
-        <is>
-          <t>35111</t>
+          <t>NEPOGODIN Aleksandr</t>
+        </is>
+      </c>
+      <c r="X585" t="inlineStr">
+        <is>
+          <t>39710</t>
         </is>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
@@ -34783,12 +34808,12 @@
       </c>
       <c r="E586" t="inlineStr">
         <is>
-          <t>Semifinal</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="F586" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G586" t="inlineStr">
@@ -34798,28 +34823,38 @@
       </c>
       <c r="H586" t="inlineStr">
         <is>
-          <t>15:34:30</t>
+          <t>15:41:00</t>
         </is>
       </c>
       <c r="I586" t="inlineStr">
         <is>
-          <t>RUS</t>
+          <t>SVK</t>
         </is>
       </c>
       <c r="J586" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K586" t="n">
         <v>565</v>
       </c>
+      <c r="M586" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N586" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="R586" t="inlineStr">
         <is>
-          <t>NEPOGODIN Aleksandr</t>
-        </is>
-      </c>
-      <c r="U586" t="inlineStr">
-        <is>
-          <t>39710</t>
+          <t>BALEJOVA Suzana</t>
+        </is>
+      </c>
+      <c r="X586" t="inlineStr">
+        <is>
+          <t>97411</t>
         </is>
       </c>
     </row>
@@ -34866,33 +34901,33 @@
       </c>
       <c r="I587" t="inlineStr">
         <is>
-          <t>SVK</t>
+          <t>RUS</t>
         </is>
       </c>
       <c r="J587" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K587" t="n">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="M587" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N587" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R587" t="inlineStr">
         <is>
-          <t>BALEJOVA Suzana</t>
-        </is>
-      </c>
-      <c r="U587" t="inlineStr">
-        <is>
-          <t>97411</t>
+          <t>KUZNETSOVA Daria</t>
+        </is>
+      </c>
+      <c r="X587" t="inlineStr">
+        <is>
+          <t>76780</t>
         </is>
       </c>
     </row>
@@ -34939,33 +34974,33 @@
       </c>
       <c r="I588" t="inlineStr">
         <is>
-          <t>RUS</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="J588" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K588" t="n">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="M588" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N588" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R588" t="inlineStr">
         <is>
-          <t>KUZNETSOVA Daria</t>
-        </is>
-      </c>
-      <c r="U588" t="inlineStr">
-        <is>
-          <t>76780</t>
+          <t>LEIBFARTH Evy</t>
+        </is>
+      </c>
+      <c r="X588" t="inlineStr">
+        <is>
+          <t>83538</t>
         </is>
       </c>
     </row>
@@ -35016,36 +35051,36 @@
         </is>
       </c>
       <c r="J589" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K589" t="n">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="M589" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N589" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R589" t="inlineStr">
         <is>
-          <t>LEIBFARTH Evy</t>
-        </is>
-      </c>
-      <c r="U589" t="inlineStr">
-        <is>
-          <t>83538</t>
+          <t>NEE Ashley</t>
+        </is>
+      </c>
+      <c r="X589" t="inlineStr">
+        <is>
+          <t>36363</t>
         </is>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
@@ -35080,38 +35115,38 @@
       </c>
       <c r="H590" t="inlineStr">
         <is>
-          <t>15:41:00</t>
+          <t>15:47:30</t>
         </is>
       </c>
       <c r="I590" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="J590" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K590" t="n">
         <v>566</v>
       </c>
       <c r="M590" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N590" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R590" t="inlineStr">
         <is>
-          <t>NEE Ashley</t>
-        </is>
-      </c>
-      <c r="U590" t="inlineStr">
-        <is>
-          <t>36363</t>
+          <t>GONCALVES Pedro</t>
+        </is>
+      </c>
+      <c r="X590" t="inlineStr">
+        <is>
+          <t>38017</t>
         </is>
       </c>
     </row>
@@ -35158,33 +35193,33 @@
       </c>
       <c r="I591" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="J591" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K591" t="n">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="M591" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N591" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R591" t="inlineStr">
         <is>
-          <t>GONCALVES Pedro</t>
-        </is>
-      </c>
-      <c r="U591" t="inlineStr">
-        <is>
-          <t>38017</t>
+          <t>HRADILEK Vavrinec</t>
+        </is>
+      </c>
+      <c r="X591" t="inlineStr">
+        <is>
+          <t>35031</t>
         </is>
       </c>
     </row>
@@ -35231,33 +35266,33 @@
       </c>
       <c r="I592" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>RUS</t>
         </is>
       </c>
       <c r="J592" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K592" t="n">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="M592" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N592" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R592" t="inlineStr">
         <is>
-          <t>HRADILEK Vavrinec</t>
-        </is>
-      </c>
-      <c r="U592" t="inlineStr">
-        <is>
-          <t>35031</t>
+          <t>NEPOGODIN Aleksandr</t>
+        </is>
+      </c>
+      <c r="X592" t="inlineStr">
+        <is>
+          <t>39710</t>
         </is>
       </c>
     </row>
@@ -35304,40 +35339,30 @@
       </c>
       <c r="I593" t="inlineStr">
         <is>
-          <t>RUS</t>
+          <t>KAZ</t>
         </is>
       </c>
       <c r="J593" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K593" t="n">
-        <v>567</v>
-      </c>
-      <c r="M593" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N593" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+        <v>566</v>
       </c>
       <c r="R593" t="inlineStr">
         <is>
-          <t>NEPOGODIN Aleksandr</t>
-        </is>
-      </c>
-      <c r="U593" t="inlineStr">
-        <is>
-          <t>39710</t>
+          <t>STANOVSKY Martin</t>
+        </is>
+      </c>
+      <c r="X593" t="inlineStr">
+        <is>
+          <t>68782</t>
         </is>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
@@ -35345,19 +35370,9 @@
           <t>SENIOR</t>
         </is>
       </c>
-      <c r="C594" t="inlineStr">
-        <is>
-          <t>K1</t>
-        </is>
-      </c>
-      <c r="D594" t="inlineStr">
-        <is>
-          <t>Cross</t>
-        </is>
-      </c>
       <c r="E594" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Forerunner</t>
         </is>
       </c>
       <c r="F594" t="inlineStr">
@@ -35372,704 +35387,21 @@
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t>15:47:30</t>
+          <t>19:10:00</t>
         </is>
       </c>
       <c r="I594" t="inlineStr">
         <is>
-          <t>KAZ</t>
+          <t>CHN</t>
         </is>
       </c>
       <c r="J594" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K594" t="n">
         <v>567</v>
       </c>
       <c r="R594" t="inlineStr">
-        <is>
-          <t>STANOVSKY Martin</t>
-        </is>
-      </c>
-      <c r="U594" t="inlineStr">
-        <is>
-          <t>68782</t>
-        </is>
-      </c>
-    </row>
-    <row r="595">
-      <c r="A595" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="B595" t="inlineStr">
-        <is>
-          <t>SENIOR</t>
-        </is>
-      </c>
-      <c r="C595" t="inlineStr">
-        <is>
-          <t>K1</t>
-        </is>
-      </c>
-      <c r="D595" t="inlineStr">
-        <is>
-          <t>Cross</t>
-        </is>
-      </c>
-      <c r="E595" t="inlineStr">
-        <is>
-          <t>Time Trials</t>
-        </is>
-      </c>
-      <c r="F595" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G595" t="inlineStr">
-        <is>
-          <t>2019-06-23</t>
-        </is>
-      </c>
-      <c r="H595" t="inlineStr">
-        <is>
-          <t>18:15:45</t>
-        </is>
-      </c>
-      <c r="I595" t="inlineStr">
-        <is>
-          <t>NED</t>
-        </is>
-      </c>
-      <c r="J595" t="n">
-        <v>5</v>
-      </c>
-      <c r="K595" t="n">
-        <v>568</v>
-      </c>
-      <c r="R595" t="inlineStr">
-        <is>
-          <t>WEGMAN Martina</t>
-        </is>
-      </c>
-      <c r="U595" t="inlineStr">
-        <is>
-          <t>35345</t>
-        </is>
-      </c>
-    </row>
-    <row r="596">
-      <c r="A596" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="B596" t="inlineStr">
-        <is>
-          <t>SENIOR</t>
-        </is>
-      </c>
-      <c r="C596" t="inlineStr">
-        <is>
-          <t>K1</t>
-        </is>
-      </c>
-      <c r="D596" t="inlineStr">
-        <is>
-          <t>Cross</t>
-        </is>
-      </c>
-      <c r="E596" t="inlineStr">
-        <is>
-          <t>Time Trials</t>
-        </is>
-      </c>
-      <c r="F596" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G596" t="inlineStr">
-        <is>
-          <t>2019-06-23</t>
-        </is>
-      </c>
-      <c r="H596" t="inlineStr">
-        <is>
-          <t>18:17:15</t>
-        </is>
-      </c>
-      <c r="I596" t="inlineStr">
-        <is>
-          <t>SVK</t>
-        </is>
-      </c>
-      <c r="J596" t="n">
-        <v>3</v>
-      </c>
-      <c r="K596" t="n">
-        <v>569</v>
-      </c>
-      <c r="R596" t="inlineStr">
-        <is>
-          <t>BALEJOVA Suzana</t>
-        </is>
-      </c>
-      <c r="U596" t="inlineStr">
-        <is>
-          <t>97411</t>
-        </is>
-      </c>
-    </row>
-    <row r="597">
-      <c r="A597" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="B597" t="inlineStr">
-        <is>
-          <t>SENIOR</t>
-        </is>
-      </c>
-      <c r="C597" t="inlineStr">
-        <is>
-          <t>K1</t>
-        </is>
-      </c>
-      <c r="D597" t="inlineStr">
-        <is>
-          <t>Cross</t>
-        </is>
-      </c>
-      <c r="E597" t="inlineStr">
-        <is>
-          <t>Time Trials</t>
-        </is>
-      </c>
-      <c r="F597" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G597" t="inlineStr">
-        <is>
-          <t>2019-06-23</t>
-        </is>
-      </c>
-      <c r="H597" t="inlineStr">
-        <is>
-          <t>18:18:00</t>
-        </is>
-      </c>
-      <c r="I597" t="inlineStr">
-        <is>
-          <t>RUS</t>
-        </is>
-      </c>
-      <c r="J597" t="n">
-        <v>2</v>
-      </c>
-      <c r="K597" t="n">
-        <v>570</v>
-      </c>
-      <c r="R597" t="inlineStr">
-        <is>
-          <t>MALEKOVA Arina</t>
-        </is>
-      </c>
-      <c r="U597" t="inlineStr">
-        <is>
-          <t>44024</t>
-        </is>
-      </c>
-    </row>
-    <row r="598">
-      <c r="A598" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="B598" t="inlineStr">
-        <is>
-          <t>SENIOR</t>
-        </is>
-      </c>
-      <c r="C598" t="inlineStr">
-        <is>
-          <t>K1</t>
-        </is>
-      </c>
-      <c r="D598" t="inlineStr">
-        <is>
-          <t>Cross</t>
-        </is>
-      </c>
-      <c r="E598" t="inlineStr">
-        <is>
-          <t>Time Trials</t>
-        </is>
-      </c>
-      <c r="F598" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G598" t="inlineStr">
-        <is>
-          <t>2019-06-23</t>
-        </is>
-      </c>
-      <c r="H598" t="inlineStr">
-        <is>
-          <t>18:26:00</t>
-        </is>
-      </c>
-      <c r="I598" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="J598" t="n">
-        <v>29</v>
-      </c>
-      <c r="K598" t="n">
-        <v>571</v>
-      </c>
-      <c r="R598" t="inlineStr">
-        <is>
-          <t>SMOLEN Michal</t>
-        </is>
-      </c>
-      <c r="U598" t="inlineStr">
-        <is>
-          <t>36397</t>
-        </is>
-      </c>
-    </row>
-    <row r="599">
-      <c r="A599" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="B599" t="inlineStr">
-        <is>
-          <t>SENIOR</t>
-        </is>
-      </c>
-      <c r="C599" t="inlineStr">
-        <is>
-          <t>K1</t>
-        </is>
-      </c>
-      <c r="D599" t="inlineStr">
-        <is>
-          <t>Cross</t>
-        </is>
-      </c>
-      <c r="E599" t="inlineStr">
-        <is>
-          <t>Time Trials</t>
-        </is>
-      </c>
-      <c r="F599" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G599" t="inlineStr">
-        <is>
-          <t>2019-06-23</t>
-        </is>
-      </c>
-      <c r="H599" t="inlineStr">
-        <is>
-          <t>18:26:45</t>
-        </is>
-      </c>
-      <c r="I599" t="inlineStr">
-        <is>
-          <t>CZE</t>
-        </is>
-      </c>
-      <c r="J599" t="n">
-        <v>28</v>
-      </c>
-      <c r="K599" t="n">
-        <v>572</v>
-      </c>
-      <c r="R599" t="inlineStr">
-        <is>
-          <t>HRADILEK Vavrinec</t>
-        </is>
-      </c>
-      <c r="U599" t="inlineStr">
-        <is>
-          <t>35031</t>
-        </is>
-      </c>
-    </row>
-    <row r="600">
-      <c r="A600" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="B600" t="inlineStr">
-        <is>
-          <t>SENIOR</t>
-        </is>
-      </c>
-      <c r="C600" t="inlineStr">
-        <is>
-          <t>K1</t>
-        </is>
-      </c>
-      <c r="D600" t="inlineStr">
-        <is>
-          <t>Cross</t>
-        </is>
-      </c>
-      <c r="E600" t="inlineStr">
-        <is>
-          <t>Time Trials</t>
-        </is>
-      </c>
-      <c r="F600" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G600" t="inlineStr">
-        <is>
-          <t>2019-06-23</t>
-        </is>
-      </c>
-      <c r="H600" t="inlineStr">
-        <is>
-          <t>18:29:00</t>
-        </is>
-      </c>
-      <c r="I600" t="inlineStr">
-        <is>
-          <t>SVK</t>
-        </is>
-      </c>
-      <c r="J600" t="n">
-        <v>25</v>
-      </c>
-      <c r="K600" t="n">
-        <v>573</v>
-      </c>
-      <c r="R600" t="inlineStr">
-        <is>
-          <t>RAJNIAK Boris</t>
-        </is>
-      </c>
-      <c r="U600" t="inlineStr">
-        <is>
-          <t>37309</t>
-        </is>
-      </c>
-    </row>
-    <row r="601">
-      <c r="A601" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="B601" t="inlineStr">
-        <is>
-          <t>SENIOR</t>
-        </is>
-      </c>
-      <c r="C601" t="inlineStr">
-        <is>
-          <t>K1</t>
-        </is>
-      </c>
-      <c r="D601" t="inlineStr">
-        <is>
-          <t>Cross</t>
-        </is>
-      </c>
-      <c r="E601" t="inlineStr">
-        <is>
-          <t>Time Trials</t>
-        </is>
-      </c>
-      <c r="F601" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G601" t="inlineStr">
-        <is>
-          <t>2019-06-23</t>
-        </is>
-      </c>
-      <c r="H601" t="inlineStr">
-        <is>
-          <t>18:30:30</t>
-        </is>
-      </c>
-      <c r="I601" t="inlineStr">
-        <is>
-          <t>CAN</t>
-        </is>
-      </c>
-      <c r="J601" t="n">
-        <v>23</v>
-      </c>
-      <c r="K601" t="n">
-        <v>574</v>
-      </c>
-      <c r="R601" t="inlineStr">
-        <is>
-          <t>HAYWARD Ben</t>
-        </is>
-      </c>
-      <c r="U601" t="inlineStr">
-        <is>
-          <t>35539</t>
-        </is>
-      </c>
-    </row>
-    <row r="602">
-      <c r="A602" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="B602" t="inlineStr">
-        <is>
-          <t>SENIOR</t>
-        </is>
-      </c>
-      <c r="C602" t="inlineStr">
-        <is>
-          <t>K1</t>
-        </is>
-      </c>
-      <c r="D602" t="inlineStr">
-        <is>
-          <t>Cross</t>
-        </is>
-      </c>
-      <c r="E602" t="inlineStr">
-        <is>
-          <t>Time Trials</t>
-        </is>
-      </c>
-      <c r="F602" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G602" t="inlineStr">
-        <is>
-          <t>2019-06-23</t>
-        </is>
-      </c>
-      <c r="H602" t="inlineStr">
-        <is>
-          <t>18:32:00</t>
-        </is>
-      </c>
-      <c r="I602" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="J602" t="n">
-        <v>21</v>
-      </c>
-      <c r="K602" t="n">
-        <v>575</v>
-      </c>
-      <c r="R602" t="inlineStr">
-        <is>
-          <t>WESTFALL Tyler</t>
-        </is>
-      </c>
-      <c r="U602" t="inlineStr">
-        <is>
-          <t>51919</t>
-        </is>
-      </c>
-    </row>
-    <row r="603">
-      <c r="A603" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="B603" t="inlineStr">
-        <is>
-          <t>SENIOR</t>
-        </is>
-      </c>
-      <c r="C603" t="inlineStr">
-        <is>
-          <t>K1</t>
-        </is>
-      </c>
-      <c r="D603" t="inlineStr">
-        <is>
-          <t>Cross</t>
-        </is>
-      </c>
-      <c r="E603" t="inlineStr">
-        <is>
-          <t>Time Trials</t>
-        </is>
-      </c>
-      <c r="F603" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G603" t="inlineStr">
-        <is>
-          <t>2019-06-23</t>
-        </is>
-      </c>
-      <c r="H603" t="inlineStr">
-        <is>
-          <t>18:36:30</t>
-        </is>
-      </c>
-      <c r="I603" t="inlineStr">
-        <is>
-          <t>THA</t>
-        </is>
-      </c>
-      <c r="J603" t="n">
-        <v>15</v>
-      </c>
-      <c r="K603" t="n">
-        <v>576</v>
-      </c>
-      <c r="R603" t="inlineStr">
-        <is>
-          <t>CHAIDET Yutthakan</t>
-        </is>
-      </c>
-      <c r="U603" t="inlineStr">
-        <is>
-          <t>51798</t>
-        </is>
-      </c>
-    </row>
-    <row r="604">
-      <c r="A604" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="B604" t="inlineStr">
-        <is>
-          <t>SENIOR</t>
-        </is>
-      </c>
-      <c r="C604" t="inlineStr">
-        <is>
-          <t>K1</t>
-        </is>
-      </c>
-      <c r="D604" t="inlineStr">
-        <is>
-          <t>Cross</t>
-        </is>
-      </c>
-      <c r="E604" t="inlineStr">
-        <is>
-          <t>Time Trials</t>
-        </is>
-      </c>
-      <c r="F604" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G604" t="inlineStr">
-        <is>
-          <t>2019-06-23</t>
-        </is>
-      </c>
-      <c r="H604" t="inlineStr">
-        <is>
-          <t>18:37:15</t>
-        </is>
-      </c>
-      <c r="I604" t="inlineStr">
-        <is>
-          <t>THA</t>
-        </is>
-      </c>
-      <c r="J604" t="n">
-        <v>14</v>
-      </c>
-      <c r="K604" t="n">
-        <v>577</v>
-      </c>
-      <c r="R604" t="inlineStr">
-        <is>
-          <t>HUSSLEIN Hermann</t>
-        </is>
-      </c>
-      <c r="U604" t="inlineStr">
-        <is>
-          <t>35462</t>
-        </is>
-      </c>
-    </row>
-    <row r="605">
-      <c r="A605" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="B605" t="inlineStr">
-        <is>
-          <t>SENIOR</t>
-        </is>
-      </c>
-      <c r="E605" t="inlineStr">
-        <is>
-          <t>Forerunner</t>
-        </is>
-      </c>
-      <c r="F605" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G605" t="inlineStr">
-        <is>
-          <t>2019-06-23</t>
-        </is>
-      </c>
-      <c r="H605" t="inlineStr">
-        <is>
-          <t>19:10:00</t>
-        </is>
-      </c>
-      <c r="I605" t="inlineStr">
-        <is>
-          <t>CHN</t>
-        </is>
-      </c>
-      <c r="J605" t="n">
-        <v>9</v>
-      </c>
-      <c r="K605" t="n">
-        <v>578</v>
-      </c>
-      <c r="R605" t="inlineStr">
         <is>
           <t>CUISHAN Yu</t>
         </is>
